--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\GSMM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\GSMM\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52C4EB8D-6911-4231-AA2F-B4D7D981ACB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA32FAE-E3BF-4526-82F2-5C62DA85B55C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23040" yWindow="12" windowWidth="23256" windowHeight="12972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RawData" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="141">
   <si>
     <t>시행년도</t>
   </si>
@@ -385,6 +385,118 @@
   </si>
   <si>
     <t>지반침하 등의 발생이력</t>
+  </si>
+  <si>
+    <t>정자동 180</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>정자동 187-7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 127</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 127-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 126</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>청솔마을사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 144</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 177</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 159</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 161</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 158</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 164</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>금곡동 157</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 23-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 9-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 23-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 23-3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 14-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 21-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미금사거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 149-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 170-2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 170-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기고속삼거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>구미동 824-4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -592,15 +704,15 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2282,8 +2394,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="100" cy="100"/>
+          <a:off x="13658850" y="63112651"/>
+          <a:ext cx="2742184" cy="1594104"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4440,7 +4552,9 @@
         <v>일반</v>
       </c>
       <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="Q6" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="R6" s="4"/>
       <c r="S6" s="5" t="s">
         <v>28</v>
@@ -4502,7 +4616,9 @@
         <v>일반</v>
       </c>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="Q7" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="R7" s="4"/>
       <c r="S7" s="5" t="s">
         <v>30</v>
@@ -4566,7 +4682,9 @@
       <c r="P8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="Q8" s="4"/>
+      <c r="Q8" s="4" t="s">
+        <v>113</v>
+      </c>
       <c r="R8" s="4"/>
       <c r="S8" s="5" t="s">
         <v>33</v>
@@ -4628,7 +4746,9 @@
         <v>일반</v>
       </c>
       <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="Q9" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="R9" s="4"/>
       <c r="S9" s="5" t="s">
         <v>35</v>
@@ -4690,7 +4810,9 @@
         <v>일반</v>
       </c>
       <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="Q10" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="R10" s="4"/>
       <c r="S10" s="5" t="s">
         <v>36</v>
@@ -4752,7 +4874,9 @@
         <v>일반</v>
       </c>
       <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
+      <c r="Q11" s="4" t="s">
+        <v>115</v>
+      </c>
       <c r="R11" s="4"/>
       <c r="S11" s="5" t="s">
         <v>37</v>
@@ -4814,7 +4938,9 @@
         <v>일반</v>
       </c>
       <c r="P12" s="4"/>
-      <c r="Q12" s="4"/>
+      <c r="Q12" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="R12" s="4"/>
       <c r="S12" s="5" t="s">
         <v>38</v>
@@ -4878,7 +5004,9 @@
       <c r="P13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q13" s="4"/>
+      <c r="Q13" s="4" t="s">
+        <v>117</v>
+      </c>
       <c r="R13" s="4"/>
       <c r="S13" s="5" t="s">
         <v>40</v>
@@ -4940,7 +5068,9 @@
         <v>일반</v>
       </c>
       <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="R14" s="4"/>
       <c r="S14" s="5" t="s">
         <v>41</v>
@@ -5002,7 +5132,9 @@
         <v>일반</v>
       </c>
       <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="4" t="s">
+        <v>119</v>
+      </c>
       <c r="R15" s="4"/>
       <c r="S15" s="5" t="s">
         <v>42</v>
@@ -5064,7 +5196,9 @@
         <v>일반</v>
       </c>
       <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="R16" s="4"/>
       <c r="S16" s="5" t="s">
         <v>43</v>
@@ -5126,7 +5260,9 @@
         <v>일반</v>
       </c>
       <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="R17" s="4"/>
       <c r="S17" s="5" t="s">
         <v>44</v>
@@ -5188,7 +5324,9 @@
         <v>일반</v>
       </c>
       <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
+      <c r="Q18" s="4" t="s">
+        <v>121</v>
+      </c>
       <c r="R18" s="4"/>
       <c r="S18" s="5" t="s">
         <v>45</v>
@@ -5250,7 +5388,9 @@
         <v>일반</v>
       </c>
       <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="4" t="s">
+        <v>122</v>
+      </c>
       <c r="R19" s="4"/>
       <c r="S19" s="5" t="s">
         <v>46</v>
@@ -5312,7 +5452,9 @@
         <v>일반</v>
       </c>
       <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="4" t="s">
+        <v>123</v>
+      </c>
       <c r="R20" s="4"/>
       <c r="S20" s="5" t="s">
         <v>48</v>
@@ -5374,7 +5516,9 @@
         <v>일반</v>
       </c>
       <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
+      <c r="Q21" s="4" t="s">
+        <v>124</v>
+      </c>
       <c r="R21" s="4"/>
       <c r="S21" s="5" t="s">
         <v>49</v>
@@ -5436,7 +5580,9 @@
         <v>일반</v>
       </c>
       <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="4" t="s">
+        <v>125</v>
+      </c>
       <c r="R22" s="4"/>
       <c r="S22" s="5" t="s">
         <v>50</v>
@@ -5498,7 +5644,9 @@
         <v>일반</v>
       </c>
       <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
+      <c r="Q23" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="R23" s="4"/>
       <c r="S23" s="5" t="s">
         <v>51</v>
@@ -5560,7 +5708,9 @@
         <v>일반</v>
       </c>
       <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
+      <c r="Q24" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="R24" s="4"/>
       <c r="S24" s="5" t="s">
         <v>52</v>
@@ -5624,7 +5774,9 @@
       <c r="P25" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Q25" s="4"/>
+      <c r="Q25" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="R25" s="4"/>
       <c r="S25" s="5" t="s">
         <v>54</v>
@@ -5686,7 +5838,9 @@
         <v>일반</v>
       </c>
       <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
+      <c r="Q26" s="4" t="s">
+        <v>127</v>
+      </c>
       <c r="R26" s="4"/>
       <c r="S26" s="5" t="s">
         <v>52</v>
@@ -5750,7 +5904,9 @@
       <c r="P27" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="Q27" s="4"/>
+      <c r="Q27" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="R27" s="4"/>
       <c r="S27" s="5" t="s">
         <v>56</v>
@@ -5814,7 +5970,9 @@
       <c r="P28" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q28" s="4"/>
+      <c r="Q28" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="R28" s="4"/>
       <c r="S28" s="5" t="s">
         <v>57</v>
@@ -5876,7 +6034,9 @@
         <v>일반</v>
       </c>
       <c r="P29" s="4"/>
-      <c r="Q29" s="4"/>
+      <c r="Q29" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="R29" s="4"/>
       <c r="S29" s="5" t="s">
         <v>58</v>
@@ -5940,7 +6100,9 @@
       <c r="P30" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Q30" s="4"/>
+      <c r="Q30" s="4" t="s">
+        <v>129</v>
+      </c>
       <c r="R30" s="4"/>
       <c r="S30" s="5" t="s">
         <v>60</v>
@@ -6004,7 +6166,9 @@
       <c r="P31" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q31" s="4"/>
+      <c r="Q31" s="4" t="s">
+        <v>130</v>
+      </c>
       <c r="R31" s="4"/>
       <c r="S31" s="5" t="s">
         <v>61</v>
@@ -6066,7 +6230,9 @@
         <v>일반</v>
       </c>
       <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
+      <c r="Q32" s="4" t="s">
+        <v>131</v>
+      </c>
       <c r="R32" s="4"/>
       <c r="S32" s="5" t="s">
         <v>62</v>
@@ -6130,7 +6296,9 @@
       <c r="P33" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q33" s="4"/>
+      <c r="Q33" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="R33" s="4"/>
       <c r="S33" s="5" t="s">
         <v>63</v>
@@ -6194,7 +6362,9 @@
       <c r="P34" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q34" s="4"/>
+      <c r="Q34" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="R34" s="4"/>
       <c r="S34" s="5" t="s">
         <v>64</v>
@@ -6256,7 +6426,9 @@
         <v>일반</v>
       </c>
       <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
+      <c r="Q35" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="R35" s="4"/>
       <c r="S35" s="5" t="s">
         <v>65</v>
@@ -6320,7 +6492,9 @@
       <c r="P36" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="Q36" s="4"/>
+      <c r="Q36" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="R36" s="4"/>
       <c r="S36" s="5" t="s">
         <v>67</v>
@@ -6382,7 +6556,9 @@
         <v>일반</v>
       </c>
       <c r="P37" s="4"/>
-      <c r="Q37" s="4"/>
+      <c r="Q37" s="4" t="s">
+        <v>134</v>
+      </c>
       <c r="R37" s="4"/>
       <c r="S37" s="5" t="s">
         <v>68</v>
@@ -6444,7 +6620,9 @@
         <v>일반</v>
       </c>
       <c r="P38" s="4"/>
-      <c r="Q38" s="4"/>
+      <c r="Q38" s="4" t="s">
+        <v>135</v>
+      </c>
       <c r="R38" s="4"/>
       <c r="S38" s="5" t="s">
         <v>69</v>
@@ -6508,7 +6686,9 @@
       <c r="P39" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="Q39" s="4"/>
+      <c r="Q39" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="R39" s="4"/>
       <c r="S39" s="5" t="s">
         <v>70</v>
@@ -6570,7 +6750,9 @@
         <v>일반</v>
       </c>
       <c r="P40" s="4"/>
-      <c r="Q40" s="4"/>
+      <c r="Q40" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="R40" s="4"/>
       <c r="S40" s="5" t="s">
         <v>72</v>
@@ -6632,7 +6814,9 @@
         <v>일반</v>
       </c>
       <c r="P41" s="4"/>
-      <c r="Q41" s="4"/>
+      <c r="Q41" s="4" t="s">
+        <v>138</v>
+      </c>
       <c r="R41" s="4"/>
       <c r="S41" s="5" t="s">
         <v>73</v>
@@ -6694,7 +6878,9 @@
         <v>일반</v>
       </c>
       <c r="P42" s="4"/>
-      <c r="Q42" s="4"/>
+      <c r="Q42" s="4" t="s">
+        <v>139</v>
+      </c>
       <c r="R42" s="4"/>
       <c r="S42" s="5" t="s">
         <v>75</v>
@@ -6756,7 +6942,9 @@
         <v>일반</v>
       </c>
       <c r="P43" s="4"/>
-      <c r="Q43" s="4"/>
+      <c r="Q43" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="R43" s="4"/>
       <c r="S43" s="5" t="s">
         <v>77</v>
@@ -7389,61 +7577,61 @@
       <c r="A4" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="23"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="23"/>
+      <c r="D4" s="24"/>
       <c r="E4" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="23"/>
+      <c r="F4" s="24"/>
       <c r="G4" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="H4" s="26"/>
-      <c r="I4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="24"/>
       <c r="J4" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="K4" s="26"/>
-      <c r="L4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="24"/>
       <c r="M4" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="N4" s="26"/>
-      <c r="O4" s="26"/>
-      <c r="P4" s="23"/>
+      <c r="N4" s="23"/>
+      <c r="O4" s="23"/>
+      <c r="P4" s="24"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="23"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="23"/>
+      <c r="D5" s="24"/>
       <c r="E5" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="F5" s="23"/>
+      <c r="F5" s="24"/>
       <c r="G5" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="26"/>
-      <c r="I5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="24"/>
       <c r="J5" s="22" t="s">
         <v>89</v>
       </c>
-      <c r="K5" s="26"/>
-      <c r="L5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="24"/>
       <c r="M5" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="N5" s="26"/>
-      <c r="O5" s="26"/>
-      <c r="P5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="23"/>
+      <c r="P5" s="24"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="9"/>
@@ -7464,43 +7652,43 @@
       <c r="P6" s="9"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
+      <c r="A7" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="27" t="s">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="24" t="s">
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="24" t="s">
+      <c r="O7" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="P7" s="24" t="s">
+      <c r="P7" s="26" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="7" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="27"/>
+      <c r="C8" s="27"/>
       <c r="D8" s="19" t="s">
         <v>8</v>
       </c>
@@ -7531,9 +7719,9 @@
       <c r="M8" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="25"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="25"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="27"/>
+      <c r="P8" s="27"/>
       <c r="Q8"/>
       <c r="R8"/>
       <c r="S8"/>
@@ -10271,6 +10459,14 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="B7:B8"/>
     <mergeCell ref="M4:P4"/>
     <mergeCell ref="I7:M7"/>
     <mergeCell ref="G5:I5"/>
@@ -10283,14 +10479,6 @@
     <mergeCell ref="N7:N8"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="B7:B8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -483,22 +483,21 @@
         <v>부가정보2</v>
       </c>
     </row>
-    <row r="5" xml:space="preserve">
+    <row r="5">
       <c r="A5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="str">
         <v>성남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-성남시-1</v>
+        <v>25-성남시-2</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
       </c>
-      <c r="E5" t="str" xml:space="preserve">
-        <v xml:space="preserve">종균열_x000d_
-횡균열</v>
+      <c r="E5" t="str">
+        <v>횡균열</v>
       </c>
       <c r="F5" t="str">
         <v>건조</v>
@@ -540,7 +539,7 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>하나은행 앞 반대도로</v>
+        <v>상록마을(임광/보성) 미켈란쉐르빌 앞 버스정류장</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -548,19 +547,19 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B6" t="str">
         <v>성남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-성남시-2</v>
+        <v>25-성남시-3</v>
       </c>
       <c r="D6" t="str">
-        <v>양호</v>
+        <v>보통</v>
       </c>
       <c r="E6" t="str">
-        <v>횡균열</v>
+        <v>-</v>
       </c>
       <c r="F6" t="str">
         <v>건조</v>
@@ -572,10 +571,10 @@
         <v>-</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -587,13 +586,13 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O6" t="str">
         <v>일반</v>
       </c>
       <c r="P6" t="str">
-        <v/>
+        <v>보도침하 8cm</v>
       </c>
       <c r="Q6" t="str">
         <v>정자동 180</v>
@@ -602,7 +601,7 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>상록마을(임광/보성) 미켈란쉐르빌 앞 버스정류장</v>
+        <v>미켈란쉐르빌 B동 앞 맞음편 보도</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -610,19 +609,19 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B7" t="str">
         <v>성남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-성남시-3</v>
+        <v>25-성남시-4</v>
       </c>
       <c r="D7" t="str">
-        <v>보통</v>
+        <v>양호</v>
       </c>
       <c r="E7" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F7" t="str">
         <v>건조</v>
@@ -634,10 +633,10 @@
         <v>-</v>
       </c>
       <c r="I7">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -655,16 +654,16 @@
         <v>일반</v>
       </c>
       <c r="P7" t="str">
-        <v>보도침하 8cm</v>
+        <v/>
       </c>
       <c r="Q7" t="str">
-        <v>정자동 180</v>
+        <v>정자동 187-7</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>미켈란쉐르빌 B동 앞 맞음편 보도</v>
+        <v>야생화지하보도 양차선도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -672,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8" t="str">
         <v>성남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-성남시-4</v>
+        <v>25-성남시-5</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -726,7 +725,7 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>야생화지하보도 양차선도로</v>
+        <v>상록마을 버스정류장 앞 양차선도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -734,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B9" t="str">
         <v>성남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-성남시-5</v>
+        <v>25-성남시-6</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -782,13 +781,13 @@
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v>정자동 187-7</v>
+        <v>금곡사거리</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>상록마을 버스정류장 앞 양차선도로</v>
+        <v>금곡사거리 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -796,19 +795,19 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B10" t="str">
         <v>성남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-성남시-6</v>
+        <v>25-성남시-7</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
       </c>
       <c r="E10" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F10" t="str">
         <v>건조</v>
@@ -823,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -835,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O10" t="str">
         <v>일반</v>
@@ -844,13 +843,13 @@
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v>금곡사거리</v>
+        <v>금곡동 127</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>금곡사거리 도로</v>
+        <v>분당경영고등학교 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -858,19 +857,19 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B11" t="str">
         <v>성남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-성남시-7</v>
+        <v>25-성남시-8</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
       </c>
       <c r="E11" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F11" t="str">
         <v>건조</v>
@@ -885,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -897,22 +896,22 @@
         <v>0</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O11" t="str">
         <v>일반</v>
       </c>
       <c r="P11" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q11" t="str">
-        <v>금곡동 127</v>
+        <v>금곡동 127-1</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>분당경영고등학교 앞 도로</v>
+        <v>#연결선 환기구 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -920,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B12" t="str">
         <v>성남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-성남시-8</v>
+        <v>25-성남시-9</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -965,16 +964,16 @@
         <v>일반</v>
       </c>
       <c r="P12" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q12" t="str">
-        <v>금곡동 127-1</v>
+        <v>금곡동 126</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>#연결선 환기구 앞 도로</v>
+        <v>청솔주공6단지 버스정류장 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -982,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="str">
         <v>성남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-성남시-9</v>
+        <v>25-성남시-10</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1030,13 +1029,13 @@
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v>금곡동 126</v>
+        <v>청솔마을사거리</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>청솔주공6단지 버스정류장 앞 도로</v>
+        <v>청솔마을 사거리 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1044,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B14" t="str">
         <v>성남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-성남시-10</v>
+        <v>25-성남시-11</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1092,13 +1091,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>청솔마을사거리</v>
+        <v>금곡동 144</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>청솔마을 사거리 앞 도로</v>
+        <v>청솔마을성원7단지 아파트707동 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1106,19 +1105,19 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="str">
         <v>성남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-성남시-11</v>
+        <v>25-성남시-12</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
       </c>
       <c r="E15" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F15" t="str">
         <v>건조</v>
@@ -1133,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1145,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15" t="str">
         <v>일반</v>
@@ -1160,7 +1159,7 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>청솔마을성원7단지 아파트707동 도로</v>
+        <v>청솔마을성원7단지 아파트706동 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1168,19 +1167,19 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B16" t="str">
         <v>성남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-성남시-12</v>
+        <v>25-성남시-13</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
       </c>
       <c r="E16" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F16" t="str">
         <v>건조</v>
@@ -1195,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1207,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" t="str">
         <v>일반</v>
@@ -1216,13 +1215,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>금곡동 144</v>
+        <v>금곡동 177</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>청솔마을성원7단지 아파트706동 도로</v>
+        <v>청솔마을 서광영남아파트103동 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1230,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="str">
         <v>성남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-성남시-13</v>
+        <v>25-성남시-14</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1278,13 +1277,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>금곡동 177</v>
+        <v>금곡동 159</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>청솔마을 서광영남아파트103동 앞 도로</v>
+        <v>GS25 분당성원점 앞 횡단보도</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1292,19 +1291,19 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" t="str">
         <v>성남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-성남시-14</v>
+        <v>25-성남시-15</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
       </c>
       <c r="E18" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F18" t="str">
         <v>건조</v>
@@ -1319,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1331,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O18" t="str">
         <v>일반</v>
@@ -1340,13 +1339,13 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>금곡동 159</v>
+        <v>금곡동 161</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>GS25 분당성원점 앞 횡단보도</v>
+        <v>옥된장 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1354,19 +1353,19 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B19" t="str">
         <v>성남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-성남시-15</v>
+        <v>25-성남시-16</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
       </c>
       <c r="E19" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F19" t="str">
         <v>건조</v>
@@ -1381,7 +1380,7 @@
         <v>0</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -1393,7 +1392,7 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O19" t="str">
         <v>일반</v>
@@ -1402,13 +1401,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>금곡동 161</v>
+        <v>금곡동 158</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>옥된장 앞 도로</v>
+        <v>올리브영 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1416,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B20" t="str">
         <v>성남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-성남시-16</v>
+        <v>25-성남시-17</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1464,13 +1463,13 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v>금곡동 158</v>
+        <v>금곡동 164</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>올리브영 앞 도로</v>
+        <v>미금역 버스정류장 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1478,13 +1477,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B21" t="str">
         <v>성남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-성남시-17</v>
+        <v>25-성남시-18</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1526,13 +1525,13 @@
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v>금곡동 164</v>
+        <v>금곡동 157</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>미금역 버스정류장 앞 도로</v>
+        <v>미금역 #1번출구 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1540,13 +1539,13 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B22" t="str">
         <v>성남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-성남시-18</v>
+        <v>25-성남시-19</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
@@ -1588,13 +1587,13 @@
         <v/>
       </c>
       <c r="Q22" t="str">
-        <v>금곡동 157</v>
+        <v>구미동 23-1</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>미금역 #1번출구 앞 도로</v>
+        <v>미금역 교차로 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1602,19 +1601,19 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B23" t="str">
         <v>성남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-성남시-19</v>
+        <v>25-성남시-20</v>
       </c>
       <c r="D23" t="str">
-        <v>양호</v>
+        <v>보통</v>
       </c>
       <c r="E23" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F23" t="str">
         <v>건조</v>
@@ -1626,10 +1625,10 @@
         <v>-</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1641,22 +1640,22 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O23" t="str">
         <v>일반</v>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>침하 5cm</v>
       </c>
       <c r="Q23" t="str">
-        <v>구미동 23-1</v>
+        <v>금곡동 157</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>미금역 교차로 도로</v>
+        <v>미금역 #2번출구 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1664,19 +1663,19 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B24" t="str">
         <v>성남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-성남시-20</v>
+        <v>25-성남시-21</v>
       </c>
       <c r="D24" t="str">
-        <v>보통</v>
+        <v>양호</v>
       </c>
       <c r="E24" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F24" t="str">
         <v>건조</v>
@@ -1688,10 +1687,10 @@
         <v>-</v>
       </c>
       <c r="I24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1703,22 +1702,22 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O24" t="str">
         <v>일반</v>
       </c>
       <c r="P24" t="str">
-        <v>침하 5cm</v>
+        <v/>
       </c>
       <c r="Q24" t="str">
-        <v>금곡동 157</v>
+        <v>구미동 23-1</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>미금역 #2번출구 앞 도로</v>
+        <v>미금역 교차로 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1726,19 +1725,19 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B25" t="str">
         <v>성남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-성남시-21</v>
+        <v>25-성남시-22</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
       </c>
       <c r="E25" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F25" t="str">
         <v>건조</v>
@@ -1753,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1765,22 +1764,22 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="str">
         <v>일반</v>
       </c>
       <c r="P25" t="str">
-        <v/>
+        <v>침하 3cm</v>
       </c>
       <c r="Q25" t="str">
-        <v>구미동 23-1</v>
+        <v>구미동 9-1</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>미금역 교차로 도로</v>
+        <v>미금역 #5출구 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1788,19 +1787,19 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B26" t="str">
         <v>성남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-성남시-22</v>
+        <v>25-성남시-23</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
       </c>
       <c r="E26" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F26" t="str">
         <v>건조</v>
@@ -1815,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -1827,22 +1826,22 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" t="str">
         <v>일반</v>
       </c>
       <c r="P26" t="str">
-        <v>침하 3cm</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q26" t="str">
-        <v>구미동 9-1</v>
+        <v>구미동 23-4</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>미금역 #5출구 앞 도로</v>
+        <v>미금역 피난계단 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1850,13 +1849,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B27" t="str">
         <v>성남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-성남시-23</v>
+        <v>25-성남시-24</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1895,16 +1894,16 @@
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q27" t="str">
-        <v>구미동 23-4</v>
+        <v>구미동 9-1</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>미금역 피난계단 앞 도로</v>
+        <v>나무수커피 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1912,19 +1911,19 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B28" t="str">
         <v>성남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-성남시-24</v>
+        <v>25-성남시-25</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
       </c>
       <c r="E28" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F28" t="str">
         <v>건조</v>
@@ -1939,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -1951,22 +1950,22 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O28" t="str">
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>침하 4cm</v>
       </c>
       <c r="Q28" t="str">
-        <v>구미동 9-1</v>
+        <v>구미동 23-4</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>나무수커피 앞 도로</v>
+        <v>택시승강장 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1974,19 +1973,19 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B29" t="str">
         <v>성남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-성남시-25</v>
+        <v>25-성남시-26</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
       </c>
       <c r="E29" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F29" t="str">
         <v>건조</v>
@@ -2001,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -2013,22 +2012,22 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O29" t="str">
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v>침하 4cm</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q29" t="str">
-        <v>구미동 23-4</v>
+        <v>구미동 23-3</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>택시승강장 앞 도로</v>
+        <v>성남고용복지 플러스센터 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2036,13 +2035,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B30" t="str">
         <v>성남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-성남시-26</v>
+        <v>25-성남시-27</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2081,16 +2080,16 @@
         <v>일반</v>
       </c>
       <c r="P30" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q30" t="str">
-        <v>구미동 23-3</v>
+        <v>구미동 14-1</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>성남고용복지 플러스센터 앞 도로</v>
+        <v>까치마을 건영빌라 503동 앞 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2098,13 +2097,13 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31" t="str">
         <v>성남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-성남시-27</v>
+        <v>25-성남시-28</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
@@ -2143,16 +2142,16 @@
         <v>일반</v>
       </c>
       <c r="P31" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q31" t="str">
-        <v>구미동 14-1</v>
+        <v>구미동 21-1</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>까치마을 건영빌라 503동 앞 도로</v>
+        <v>까치마을 건영빌라 303동 앞 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2160,19 +2159,19 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B32" t="str">
         <v>성남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-성남시-28</v>
+        <v>25-성남시-29</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
       </c>
       <c r="E32" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F32" t="str">
         <v>건조</v>
@@ -2186,8 +2185,8 @@
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32">
-        <v>3</v>
+      <c r="J32" t="b">
+        <v>0</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2199,7 +2198,7 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O32" t="str">
         <v>일반</v>
@@ -2214,7 +2213,7 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>까치마을 건영빌라 303동 앞 도로</v>
+        <v>까치마을 건영빌라 302동 앞 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2222,19 +2221,19 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B33" t="str">
         <v>성남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-성남시-29</v>
+        <v>25-성남시-30</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
       </c>
       <c r="E33" t="str">
-        <v>양호</v>
+        <v>횡균열</v>
       </c>
       <c r="F33" t="str">
         <v>건조</v>
@@ -2248,8 +2247,8 @@
       <c r="I33">
         <v>0</v>
       </c>
-      <c r="J33" t="b">
-        <v>0</v>
+      <c r="J33">
+        <v>1</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2261,13 +2260,13 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O33" t="str">
         <v>일반</v>
       </c>
       <c r="P33" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q33" t="str">
         <v>구미동 21-1</v>
@@ -2276,7 +2275,7 @@
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>까치마을 건영빌라 302동 앞 도로</v>
+        <v>까치마을 지하보도 도로</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2284,19 +2283,19 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B34" t="str">
         <v>성남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-성남시-30</v>
+        <v>25-성남시-31</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
       </c>
       <c r="E34" t="str">
-        <v>횡균열</v>
+        <v>-</v>
       </c>
       <c r="F34" t="str">
         <v>건조</v>
@@ -2311,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2323,22 +2322,22 @@
         <v>0</v>
       </c>
       <c r="N34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O34" t="str">
         <v>일반</v>
       </c>
       <c r="P34" t="str">
-        <v/>
+        <v>침하 2cm</v>
       </c>
       <c r="Q34" t="str">
-        <v>구미동 21-1</v>
+        <v>구미동 13</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>까치마을 지하보도 도로</v>
+        <v>까치마을 건영빌라 603동 앞 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2346,19 +2345,19 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" t="str">
         <v>성남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-성남시-31</v>
+        <v>25-성남시-32</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
       </c>
       <c r="E35" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F35" t="str">
         <v>건조</v>
@@ -2373,7 +2372,7 @@
         <v>0</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -2385,22 +2384,22 @@
         <v>0</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O35" t="str">
         <v>일반</v>
       </c>
       <c r="P35" t="str">
-        <v>침하 2cm</v>
+        <v/>
       </c>
       <c r="Q35" t="str">
-        <v>구미동 13</v>
+        <v>미금사거리</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>까치마을 건영빌라 603동 앞 도로</v>
+        <v>미금사거리 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2408,13 +2407,13 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" t="str">
         <v>성남대로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-성남시-32</v>
+        <v>25-성남시-33</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
@@ -2456,13 +2455,13 @@
         <v/>
       </c>
       <c r="Q36" t="str">
-        <v>미금사거리</v>
+        <v>구미동 17</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>미금사거리 도로</v>
+        <v>성남구미도서관 앞 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2470,13 +2469,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B37" t="str">
         <v>성남대로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-성남시-33</v>
+        <v>25-성남시-34</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2515,16 +2514,16 @@
         <v>일반</v>
       </c>
       <c r="P37" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q37" t="str">
-        <v>구미동 17</v>
+        <v>구미동 149-1</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>성남구미도서관 앞 도로</v>
+        <v>서울그린빌 1동 앞 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2532,13 +2531,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B38" t="str">
-        <v>성남대로</v>
+        <v>탄천상로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-성남시-34</v>
+        <v>25-성남시-35</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2577,16 +2576,16 @@
         <v>일반</v>
       </c>
       <c r="P38" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q38" t="str">
-        <v>구미동 149-1</v>
+        <v>구미동 170-2</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>서울그린빌 1동 앞 도로</v>
+        <v>동막교 앞 사거리 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2594,13 +2593,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B39" t="str">
         <v>탄천상로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-성남시-35</v>
+        <v>25-성남시-36</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2642,13 +2641,13 @@
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v>구미동 170-2</v>
+        <v>구미동 170-1</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>동막교 앞 사거리 도로</v>
+        <v>KD운송그룹 분당영업소 앞 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2656,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B40" t="str">
-        <v>탄천상로</v>
+        <v>분당수서로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-성남시-36</v>
+        <v>25-성남시-37</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2704,13 +2703,13 @@
         <v/>
       </c>
       <c r="Q40" t="str">
-        <v>구미동 170-1</v>
+        <v>경기고속삼거리</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>KD운송그룹 분당영업소 앞 도로</v>
+        <v>경기고속 삼거리 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2718,13 +2717,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B41" t="str">
-        <v>분당수서로</v>
+        <v>신수로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-성남시-37</v>
+        <v>25-성남시-38</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2766,27 +2765,27 @@
         <v/>
       </c>
       <c r="Q41" t="str">
-        <v>경기고속삼거리</v>
+        <v>구미동 824-4</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>경기고속 삼거리 도로</v>
+        <v>강원철물건재 앞 도로</v>
       </c>
       <c r="T41" t="str">
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>38</v>
+      <c r="A42" t="str">
+        <v>26-01</v>
       </c>
       <c r="B42" t="str">
-        <v>신수로</v>
+        <v>성남대로</v>
       </c>
       <c r="C42" t="str">
-        <v>25-성남시-38</v>
+        <v>26-성남시-01</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
@@ -2795,46 +2794,46 @@
         <v>거북등</v>
       </c>
       <c r="F42" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G42" t="str">
-        <v>9.3</v>
+        <v>10.3</v>
       </c>
       <c r="H42" t="str">
         <v>-</v>
       </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>3</v>
-      </c>
-      <c r="K42">
-        <v>0</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>3</v>
+      <c r="I42" t="str">
+        <v>0</v>
+      </c>
+      <c r="J42" t="str">
+        <v>3</v>
+      </c>
+      <c r="K42" t="str">
+        <v>0</v>
+      </c>
+      <c r="L42" t="str">
+        <v>1</v>
+      </c>
+      <c r="M42" t="str">
+        <v>0</v>
+      </c>
+      <c r="N42" t="str">
+        <v>4</v>
       </c>
       <c r="O42" t="str">
         <v>일반</v>
       </c>
       <c r="P42" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q42" t="str">
-        <v>구미동 824-4</v>
+        <v>정자동180</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>강원철물건재 앞 도로</v>
+        <v>미켈란쉐르빌아파트 앞 양차선(정자일로100)</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2842,19 +2841,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B43" t="str">
         <v>성남대로</v>
       </c>
       <c r="C43" t="str">
-        <v>26-성남시-01</v>
+        <v>26-성남시-02</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
       </c>
       <c r="E43" t="str">
-        <v>거북등</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F43" t="str">
         <v>양호</v>
@@ -2869,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K43" t="str">
         <v>0</v>
@@ -2881,7 +2880,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O43" t="str">
         <v>일반</v>
@@ -2890,13 +2889,13 @@
         <v>-</v>
       </c>
       <c r="Q43" t="str">
-        <v>정자동180</v>
+        <v>정자동181</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>미켈란쉐르빌아파트 앞 양차선(정자일로100)</v>
+        <v>상록마을 임광보성아파트 406동 앞 도로(정자일로80)</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2904,19 +2903,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B44" t="str">
         <v>성남대로</v>
       </c>
       <c r="C44" t="str">
-        <v>26-성남시-02</v>
+        <v>26-성남시-03</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
       </c>
       <c r="E44" t="str">
-        <v>종,횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F44" t="str">
         <v>양호</v>
@@ -2949,7 +2948,7 @@
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v>-</v>
+        <v>5cm이하 침하(바퀴자리)</v>
       </c>
       <c r="Q44" t="str">
         <v>정자동181</v>
@@ -2958,7 +2957,7 @@
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>상록마을 임광보성아파트 406동 앞 도로(정자일로80)</v>
+        <v>상록마을 임광보성아파트 408동 앞 도로(정자일로80)</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2966,19 +2965,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B45" t="str">
         <v>성남대로</v>
       </c>
       <c r="C45" t="str">
-        <v>26-성남시-03</v>
+        <v>26-성남시-04</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
       </c>
       <c r="E45" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F45" t="str">
         <v>양호</v>
@@ -2993,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K45" t="str">
         <v>0</v>
@@ -3005,22 +3004,22 @@
         <v>0</v>
       </c>
       <c r="N45" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O45" t="str">
         <v>일반</v>
       </c>
       <c r="P45" t="str">
-        <v>5cm이하 침하(바퀴자리)</v>
+        <v>-</v>
       </c>
       <c r="Q45" t="str">
-        <v>정자동181</v>
+        <v>금곡사거리</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>상록마을 임광보성아파트 408동 앞 도로(정자일로80)</v>
+        <v>금곡사거리</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3028,13 +3027,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B46" t="str">
         <v>성남대로</v>
       </c>
       <c r="C46" t="str">
-        <v>26-성남시-04</v>
+        <v>26-성남시-05</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
@@ -3076,13 +3075,13 @@
         <v>-</v>
       </c>
       <c r="Q46" t="str">
-        <v>금곡사거리</v>
+        <v>청솔마을 사거리</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>금곡사거리</v>
+        <v>청솔마을사거리</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3090,19 +3089,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B47" t="str">
         <v>성남대로</v>
       </c>
       <c r="C47" t="str">
-        <v>26-성남시-05</v>
+        <v>26-성남시-06</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F47" t="str">
         <v>양호</v>
@@ -3117,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K47" t="str">
         <v>0</v>
@@ -3129,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O47" t="str">
         <v>일반</v>
@@ -3138,33 +3137,33 @@
         <v>-</v>
       </c>
       <c r="Q47" t="str">
-        <v>청솔마을 사거리</v>
+        <v>금곡동176</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>청솔마을사거리</v>
+        <v>청솔마을계룡아파트 112동 앞 도로(정자일로30)</v>
       </c>
       <c r="T47" t="str">
-        <v/>
+        <v>현장확인필요</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B48" t="str">
         <v>성남대로</v>
       </c>
       <c r="C48" t="str">
-        <v>26-성남시-06</v>
+        <v>26-성남시-07</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F48" t="str">
         <v>양호</v>
@@ -3206,7 +3205,7 @@
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>청솔마을계룡아파트 112동 앞 도로(정자일로30)</v>
+        <v>청솔마을계룡아파트 어린이놀이터 앞 도로(정자일로30)</v>
       </c>
       <c r="T48" t="str">
         <v>현장확인필요</v>
@@ -3214,19 +3213,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B49" t="str">
         <v>성남대로</v>
       </c>
       <c r="C49" t="str">
-        <v>26-성남시-07</v>
+        <v>26-성남시-08</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
       </c>
       <c r="E49" t="str">
-        <v>종균열</v>
+        <v>종횡균열</v>
       </c>
       <c r="F49" t="str">
         <v>양호</v>
@@ -3259,78 +3258,78 @@
         <v>일반</v>
       </c>
       <c r="P49" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q49" t="str">
-        <v>금곡동176</v>
+        <v>금곡동177</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>청솔마을계룡아파트 어린이놀이터 앞 도로(정자일로30)</v>
+        <v>청솔마을서광영남아파트 101동 앞 도로(성남대로171번길8</v>
       </c>
       <c r="T49" t="str">
         <v>현장확인필요</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="str">
-        <v>26-08</v>
+      <c r="A50">
+        <v>73712</v>
       </c>
       <c r="B50" t="str">
-        <v>성남대로</v>
+        <v>수동추가</v>
       </c>
       <c r="C50" t="str">
-        <v>26-성남시-08</v>
+        <v>ADD</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
       </c>
       <c r="E50" t="str">
-        <v>종횡균열</v>
+        <v>양호</v>
       </c>
       <c r="F50" t="str">
         <v>양호</v>
       </c>
       <c r="G50" t="str">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="H50" t="str">
         <v>-</v>
       </c>
       <c r="I50" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="J50" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="K50" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="L50" t="str">
-        <v>1</v>
+        <v/>
       </c>
       <c r="M50" t="str">
-        <v>0</v>
+        <v/>
       </c>
       <c r="N50" t="str">
-        <v>2</v>
+        <v/>
       </c>
       <c r="O50" t="str">
         <v>일반</v>
       </c>
       <c r="P50" t="str">
-        <v>5cm이하 침하</v>
+        <v/>
       </c>
       <c r="Q50" t="str">
-        <v>금곡동177</v>
+        <v>분당구 금곡동177</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>청솔마을서광영남아파트 101동 앞 도로(성남대로171번길8</v>
+        <v>직접입력</v>
       </c>
       <c r="T50" t="str">
         <v>현장확인필요</v>

--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T50"/>
+  <dimension ref="A1:T49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,19 +485,19 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="str">
         <v>성남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-성남시-2</v>
+        <v>25-성남시-3</v>
       </c>
       <c r="D5" t="str">
-        <v>양호</v>
+        <v>보통</v>
       </c>
       <c r="E5" t="str">
-        <v>횡균열</v>
+        <v>-</v>
       </c>
       <c r="F5" t="str">
         <v>건조</v>
@@ -509,10 +509,10 @@
         <v>-</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -524,13 +524,13 @@
         <v>0</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O5" t="str">
         <v>일반</v>
       </c>
       <c r="P5" t="str">
-        <v/>
+        <v>보도침하 8cm</v>
       </c>
       <c r="Q5" t="str">
         <v>정자동 180</v>
@@ -539,7 +539,7 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>상록마을(임광/보성) 미켈란쉐르빌 앞 버스정류장</v>
+        <v>미켈란쉐르빌 B동 앞 맞음편 보도</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,19 +547,19 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="str">
         <v>성남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-성남시-3</v>
+        <v>25-성남시-4</v>
       </c>
       <c r="D6" t="str">
-        <v>보통</v>
+        <v>양호</v>
       </c>
       <c r="E6" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F6" t="str">
         <v>건조</v>
@@ -571,10 +571,10 @@
         <v>-</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -592,16 +592,16 @@
         <v>일반</v>
       </c>
       <c r="P6" t="str">
-        <v>보도침하 8cm</v>
+        <v/>
       </c>
       <c r="Q6" t="str">
-        <v>정자동 180</v>
+        <v>정자동 187-7</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>미켈란쉐르빌 B동 앞 맞음편 보도</v>
+        <v>야생화지하보도 양차선도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="str">
         <v>성남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-성남시-4</v>
+        <v>25-성남시-5</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -663,7 +663,7 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>야생화지하보도 양차선도로</v>
+        <v>상록마을 버스정류장 앞 양차선도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,13 +671,13 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="str">
         <v>성남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-성남시-5</v>
+        <v>25-성남시-6</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
@@ -719,13 +719,13 @@
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v>정자동 187-7</v>
+        <v>금곡사거리</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>상록마을 버스정류장 앞 양차선도로</v>
+        <v>금곡사거리 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,19 +733,19 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="str">
         <v>성남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-성남시-6</v>
+        <v>25-성남시-7</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
       </c>
       <c r="E9" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F9" t="str">
         <v>건조</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -772,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O9" t="str">
         <v>일반</v>
@@ -781,13 +781,13 @@
         <v/>
       </c>
       <c r="Q9" t="str">
-        <v>금곡사거리</v>
+        <v>금곡동 127</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>금곡사거리 도로</v>
+        <v>분당경영고등학교 앞 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,19 +795,19 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="str">
         <v>성남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-성남시-7</v>
+        <v>25-성남시-8</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
       </c>
       <c r="E10" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F10" t="str">
         <v>건조</v>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -834,22 +834,22 @@
         <v>0</v>
       </c>
       <c r="N10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O10" t="str">
         <v>일반</v>
       </c>
       <c r="P10" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q10" t="str">
-        <v>금곡동 127</v>
+        <v>금곡동 127-1</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>분당경영고등학교 앞 도로</v>
+        <v>#연결선 환기구 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="str">
         <v>성남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-성남시-8</v>
+        <v>25-성남시-9</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -902,16 +902,16 @@
         <v>일반</v>
       </c>
       <c r="P11" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q11" t="str">
-        <v>금곡동 127-1</v>
+        <v>금곡동 126</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>#연결선 환기구 앞 도로</v>
+        <v>청솔주공6단지 버스정류장 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="str">
         <v>성남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-성남시-9</v>
+        <v>25-성남시-10</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -967,13 +967,13 @@
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v>금곡동 126</v>
+        <v>청솔마을사거리</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>청솔주공6단지 버스정류장 앞 도로</v>
+        <v>청솔마을 사거리 앞 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,13 +981,13 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" t="str">
         <v>성남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-성남시-10</v>
+        <v>25-성남시-11</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
@@ -1029,13 +1029,13 @@
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v>청솔마을사거리</v>
+        <v>금곡동 144</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>청솔마을 사거리 앞 도로</v>
+        <v>청솔마을성원7단지 아파트707동 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,19 +1043,19 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14" t="str">
         <v>성남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-성남시-11</v>
+        <v>25-성남시-12</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
       </c>
       <c r="E14" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F14" t="str">
         <v>건조</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O14" t="str">
         <v>일반</v>
@@ -1097,7 +1097,7 @@
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>청솔마을성원7단지 아파트707동 도로</v>
+        <v>청솔마을성원7단지 아파트706동 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,19 +1105,19 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B15" t="str">
         <v>성남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-성남시-12</v>
+        <v>25-성남시-13</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
       </c>
       <c r="E15" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F15" t="str">
         <v>건조</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O15" t="str">
         <v>일반</v>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>금곡동 144</v>
+        <v>금곡동 177</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>청솔마을성원7단지 아파트706동 도로</v>
+        <v>청솔마을 서광영남아파트103동 앞 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,13 +1167,13 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B16" t="str">
         <v>성남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-성남시-13</v>
+        <v>25-성남시-14</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
@@ -1215,13 +1215,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>금곡동 177</v>
+        <v>금곡동 159</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>청솔마을 서광영남아파트103동 앞 도로</v>
+        <v>GS25 분당성원점 앞 횡단보도</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,19 +1229,19 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B17" t="str">
         <v>성남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-성남시-14</v>
+        <v>25-성남시-15</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
       </c>
       <c r="E17" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F17" t="str">
         <v>건조</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O17" t="str">
         <v>일반</v>
@@ -1277,13 +1277,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>금곡동 159</v>
+        <v>금곡동 161</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>GS25 분당성원점 앞 횡단보도</v>
+        <v>옥된장 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,19 +1291,19 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B18" t="str">
         <v>성남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-성남시-15</v>
+        <v>25-성남시-16</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
       </c>
       <c r="E18" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F18" t="str">
         <v>건조</v>
@@ -1318,7 +1318,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -1330,7 +1330,7 @@
         <v>0</v>
       </c>
       <c r="N18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O18" t="str">
         <v>일반</v>
@@ -1339,13 +1339,13 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>금곡동 161</v>
+        <v>금곡동 158</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>옥된장 앞 도로</v>
+        <v>올리브영 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B19" t="str">
         <v>성남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-성남시-16</v>
+        <v>25-성남시-17</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>금곡동 158</v>
+        <v>금곡동 164</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>올리브영 앞 도로</v>
+        <v>미금역 버스정류장 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B20" t="str">
         <v>성남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-성남시-17</v>
+        <v>25-성남시-18</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1463,13 +1463,13 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v>금곡동 164</v>
+        <v>금곡동 157</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>미금역 버스정류장 앞 도로</v>
+        <v>미금역 #1번출구 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,13 +1477,13 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B21" t="str">
         <v>성남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-성남시-18</v>
+        <v>25-성남시-19</v>
       </c>
       <c r="D21" t="str">
         <v>양호</v>
@@ -1525,13 +1525,13 @@
         <v/>
       </c>
       <c r="Q21" t="str">
-        <v>금곡동 157</v>
+        <v>구미동 23-1</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>미금역 #1번출구 앞 도로</v>
+        <v>미금역 교차로 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,19 +1539,19 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B22" t="str">
         <v>성남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-성남시-19</v>
+        <v>25-성남시-20</v>
       </c>
       <c r="D22" t="str">
-        <v>양호</v>
+        <v>보통</v>
       </c>
       <c r="E22" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F22" t="str">
         <v>건조</v>
@@ -1563,10 +1563,10 @@
         <v>-</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1578,22 +1578,22 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O22" t="str">
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>침하 5cm</v>
       </c>
       <c r="Q22" t="str">
-        <v>구미동 23-1</v>
+        <v>금곡동 157</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>미금역 교차로 도로</v>
+        <v>미금역 #2번출구 앞 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B23" t="str">
         <v>성남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-성남시-20</v>
+        <v>25-성남시-21</v>
       </c>
       <c r="D23" t="str">
-        <v>보통</v>
+        <v>양호</v>
       </c>
       <c r="E23" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F23" t="str">
         <v>건조</v>
@@ -1625,10 +1625,10 @@
         <v>-</v>
       </c>
       <c r="I23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1640,22 +1640,22 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O23" t="str">
         <v>일반</v>
       </c>
       <c r="P23" t="str">
-        <v>침하 5cm</v>
+        <v/>
       </c>
       <c r="Q23" t="str">
-        <v>금곡동 157</v>
+        <v>구미동 23-1</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>미금역 #2번출구 앞 도로</v>
+        <v>미금역 교차로 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,19 +1663,19 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B24" t="str">
         <v>성남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-성남시-21</v>
+        <v>25-성남시-22</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
       </c>
       <c r="E24" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F24" t="str">
         <v>건조</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1702,22 +1702,22 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O24" t="str">
         <v>일반</v>
       </c>
       <c r="P24" t="str">
-        <v/>
+        <v>침하 3cm</v>
       </c>
       <c r="Q24" t="str">
-        <v>구미동 23-1</v>
+        <v>구미동 9-1</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>미금역 교차로 도로</v>
+        <v>미금역 #5출구 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,19 +1725,19 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B25" t="str">
         <v>성남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-성남시-22</v>
+        <v>25-성남시-23</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
       </c>
       <c r="E25" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F25" t="str">
         <v>건조</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1764,22 +1764,22 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O25" t="str">
         <v>일반</v>
       </c>
       <c r="P25" t="str">
-        <v>침하 3cm</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q25" t="str">
-        <v>구미동 9-1</v>
+        <v>구미동 23-4</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>미금역 #5출구 앞 도로</v>
+        <v>미금역 피난계단 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,13 +1787,13 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B26" t="str">
         <v>성남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-성남시-23</v>
+        <v>25-성남시-24</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
@@ -1832,16 +1832,16 @@
         <v>일반</v>
       </c>
       <c r="P26" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q26" t="str">
-        <v>구미동 23-4</v>
+        <v>구미동 9-1</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>미금역 피난계단 앞 도로</v>
+        <v>나무수커피 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,19 +1849,19 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B27" t="str">
         <v>성남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-성남시-24</v>
+        <v>25-성남시-25</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
       </c>
       <c r="E27" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F27" t="str">
         <v>건조</v>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O27" t="str">
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v/>
+        <v>침하 4cm</v>
       </c>
       <c r="Q27" t="str">
-        <v>구미동 9-1</v>
+        <v>구미동 23-4</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>나무수커피 앞 도로</v>
+        <v>택시승강장 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,19 +1911,19 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B28" t="str">
         <v>성남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-성남시-25</v>
+        <v>25-성남시-26</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
       </c>
       <c r="E28" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F28" t="str">
         <v>건조</v>
@@ -1938,7 +1938,7 @@
         <v>0</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K28">
         <v>0</v>
@@ -1950,22 +1950,22 @@
         <v>0</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O28" t="str">
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v>침하 4cm</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q28" t="str">
-        <v>구미동 23-4</v>
+        <v>구미동 23-3</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>택시승강장 앞 도로</v>
+        <v>성남고용복지 플러스센터 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B29" t="str">
         <v>성남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-성남시-26</v>
+        <v>25-성남시-27</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2018,16 +2018,16 @@
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q29" t="str">
-        <v>구미동 23-3</v>
+        <v>구미동 14-1</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>성남고용복지 플러스센터 앞 도로</v>
+        <v>까치마을 건영빌라 503동 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,13 +2035,13 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30" t="str">
         <v>성남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-성남시-27</v>
+        <v>25-성남시-28</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
@@ -2080,16 +2080,16 @@
         <v>일반</v>
       </c>
       <c r="P30" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q30" t="str">
-        <v>구미동 14-1</v>
+        <v>구미동 21-1</v>
       </c>
       <c r="R30" t="str">
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>까치마을 건영빌라 503동 앞 도로</v>
+        <v>까치마을 건영빌라 303동 앞 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,19 +2097,19 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B31" t="str">
         <v>성남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-성남시-28</v>
+        <v>25-성남시-29</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
       </c>
       <c r="E31" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F31" t="str">
         <v>건조</v>
@@ -2123,8 +2123,8 @@
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31">
-        <v>3</v>
+      <c r="J31" t="b">
+        <v>0</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O31" t="str">
         <v>일반</v>
@@ -2151,7 +2151,7 @@
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>까치마을 건영빌라 303동 앞 도로</v>
+        <v>까치마을 건영빌라 302동 앞 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,19 +2159,19 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B32" t="str">
         <v>성남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-성남시-29</v>
+        <v>25-성남시-30</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
       </c>
       <c r="E32" t="str">
-        <v>양호</v>
+        <v>횡균열</v>
       </c>
       <c r="F32" t="str">
         <v>건조</v>
@@ -2185,8 +2185,8 @@
       <c r="I32">
         <v>0</v>
       </c>
-      <c r="J32" t="b">
-        <v>0</v>
+      <c r="J32">
+        <v>1</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2198,13 +2198,13 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="str">
         <v>일반</v>
       </c>
       <c r="P32" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q32" t="str">
         <v>구미동 21-1</v>
@@ -2213,7 +2213,7 @@
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>까치마을 건영빌라 302동 앞 도로</v>
+        <v>까치마을 지하보도 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B33" t="str">
         <v>성남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-성남시-30</v>
+        <v>25-성남시-31</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
       </c>
       <c r="E33" t="str">
-        <v>횡균열</v>
+        <v>-</v>
       </c>
       <c r="F33" t="str">
         <v>건조</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2260,22 +2260,22 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O33" t="str">
         <v>일반</v>
       </c>
       <c r="P33" t="str">
-        <v/>
+        <v>침하 2cm</v>
       </c>
       <c r="Q33" t="str">
-        <v>구미동 21-1</v>
+        <v>구미동 13</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>까치마을 지하보도 도로</v>
+        <v>까치마을 건영빌라 603동 앞 도로</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,19 +2283,19 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" t="str">
         <v>성남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-성남시-31</v>
+        <v>25-성남시-32</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
       </c>
       <c r="E34" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F34" t="str">
         <v>건조</v>
@@ -2310,7 +2310,7 @@
         <v>0</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -2322,22 +2322,22 @@
         <v>0</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O34" t="str">
         <v>일반</v>
       </c>
       <c r="P34" t="str">
-        <v>침하 2cm</v>
+        <v/>
       </c>
       <c r="Q34" t="str">
-        <v>구미동 13</v>
+        <v>미금사거리</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>까치마을 건영빌라 603동 앞 도로</v>
+        <v>미금사거리 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,13 +2345,13 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" t="str">
         <v>성남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-성남시-32</v>
+        <v>25-성남시-33</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
@@ -2393,13 +2393,13 @@
         <v/>
       </c>
       <c r="Q35" t="str">
-        <v>미금사거리</v>
+        <v>구미동 17</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>미금사거리 도로</v>
+        <v>성남구미도서관 앞 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,13 +2407,13 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="str">
         <v>성남대로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-성남시-33</v>
+        <v>25-성남시-34</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
@@ -2452,16 +2452,16 @@
         <v>일반</v>
       </c>
       <c r="P36" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q36" t="str">
-        <v>구미동 17</v>
+        <v>구미동 149-1</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>성남구미도서관 앞 도로</v>
+        <v>서울그린빌 1동 앞 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,13 +2469,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B37" t="str">
-        <v>성남대로</v>
+        <v>탄천상로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-성남시-34</v>
+        <v>25-성남시-35</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2514,16 +2514,16 @@
         <v>일반</v>
       </c>
       <c r="P37" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q37" t="str">
-        <v>구미동 149-1</v>
+        <v>구미동 170-2</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>서울그린빌 1동 앞 도로</v>
+        <v>동막교 앞 사거리 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B38" t="str">
         <v>탄천상로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-성남시-35</v>
+        <v>25-성남시-36</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>구미동 170-2</v>
+        <v>구미동 170-1</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>동막교 앞 사거리 도로</v>
+        <v>KD운송그룹 분당영업소 앞 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B39" t="str">
-        <v>탄천상로</v>
+        <v>분당수서로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-성남시-36</v>
+        <v>25-성남시-37</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2641,13 +2641,13 @@
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v>구미동 170-1</v>
+        <v>경기고속삼거리</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>KD운송그룹 분당영업소 앞 도로</v>
+        <v>경기고속 삼거리 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,13 +2655,13 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B40" t="str">
-        <v>분당수서로</v>
+        <v>신수로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-성남시-37</v>
+        <v>25-성남시-38</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2703,27 +2703,27 @@
         <v/>
       </c>
       <c r="Q40" t="str">
-        <v>경기고속삼거리</v>
+        <v>구미동 824-4</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>경기고속 삼거리 도로</v>
+        <v>강원철물건재 앞 도로</v>
       </c>
       <c r="T40" t="str">
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>38</v>
+      <c r="A41" t="str">
+        <v>26-01</v>
       </c>
       <c r="B41" t="str">
-        <v>신수로</v>
+        <v>성남대로</v>
       </c>
       <c r="C41" t="str">
-        <v>25-성남시-38</v>
+        <v>26-성남시-01</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
@@ -2732,46 +2732,46 @@
         <v>거북등</v>
       </c>
       <c r="F41" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G41" t="str">
-        <v>9.3</v>
+        <v>10.3</v>
       </c>
       <c r="H41" t="str">
         <v>-</v>
       </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>3</v>
-      </c>
-      <c r="K41">
-        <v>0</v>
-      </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>0</v>
-      </c>
-      <c r="N41">
-        <v>3</v>
+      <c r="I41" t="str">
+        <v>0</v>
+      </c>
+      <c r="J41" t="str">
+        <v>3</v>
+      </c>
+      <c r="K41" t="str">
+        <v>0</v>
+      </c>
+      <c r="L41" t="str">
+        <v>1</v>
+      </c>
+      <c r="M41" t="str">
+        <v>0</v>
+      </c>
+      <c r="N41" t="str">
+        <v>4</v>
       </c>
       <c r="O41" t="str">
         <v>일반</v>
       </c>
       <c r="P41" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q41" t="str">
-        <v>구미동 824-4</v>
+        <v>정자동180</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>강원철물건재 앞 도로</v>
+        <v>미켈란쉐르빌아파트 앞 양차선(정자일로100)</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,19 +2779,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B42" t="str">
         <v>성남대로</v>
       </c>
       <c r="C42" t="str">
-        <v>26-성남시-01</v>
+        <v>26-성남시-02</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
       </c>
       <c r="E42" t="str">
-        <v>거북등</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F42" t="str">
         <v>양호</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K42" t="str">
         <v>0</v>
@@ -2818,7 +2818,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O42" t="str">
         <v>일반</v>
@@ -2827,13 +2827,13 @@
         <v>-</v>
       </c>
       <c r="Q42" t="str">
-        <v>정자동180</v>
+        <v>정자동181</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>미켈란쉐르빌아파트 앞 양차선(정자일로100)</v>
+        <v>상록마을 임광보성아파트 406동 앞 도로(정자일로80)</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,19 +2841,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B43" t="str">
         <v>성남대로</v>
       </c>
       <c r="C43" t="str">
-        <v>26-성남시-02</v>
+        <v>26-성남시-03</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
       </c>
       <c r="E43" t="str">
-        <v>종,횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F43" t="str">
         <v>양호</v>
@@ -2886,7 +2886,7 @@
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v>-</v>
+        <v>5cm이하 침하(바퀴자리)</v>
       </c>
       <c r="Q43" t="str">
         <v>정자동181</v>
@@ -2895,7 +2895,7 @@
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>상록마을 임광보성아파트 406동 앞 도로(정자일로80)</v>
+        <v>상록마을 임광보성아파트 408동 앞 도로(정자일로80)</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,19 +2903,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B44" t="str">
         <v>성남대로</v>
       </c>
       <c r="C44" t="str">
-        <v>26-성남시-03</v>
+        <v>26-성남시-04</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
       </c>
       <c r="E44" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F44" t="str">
         <v>양호</v>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K44" t="str">
         <v>0</v>
@@ -2942,22 +2942,22 @@
         <v>0</v>
       </c>
       <c r="N44" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O44" t="str">
         <v>일반</v>
       </c>
       <c r="P44" t="str">
-        <v>5cm이하 침하(바퀴자리)</v>
+        <v>-</v>
       </c>
       <c r="Q44" t="str">
-        <v>정자동181</v>
+        <v>금곡사거리</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>상록마을 임광보성아파트 408동 앞 도로(정자일로80)</v>
+        <v>금곡사거리</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,13 +2965,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B45" t="str">
         <v>성남대로</v>
       </c>
       <c r="C45" t="str">
-        <v>26-성남시-04</v>
+        <v>26-성남시-05</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
@@ -3013,13 +3013,13 @@
         <v>-</v>
       </c>
       <c r="Q45" t="str">
-        <v>금곡사거리</v>
+        <v>청솔마을 사거리</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>금곡사거리</v>
+        <v>청솔마을사거리</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,19 +3027,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B46" t="str">
         <v>성남대로</v>
       </c>
       <c r="C46" t="str">
-        <v>26-성남시-05</v>
+        <v>26-성남시-06</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
       </c>
       <c r="E46" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F46" t="str">
         <v>양호</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K46" t="str">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O46" t="str">
         <v>일반</v>
@@ -3075,33 +3075,33 @@
         <v>-</v>
       </c>
       <c r="Q46" t="str">
-        <v>청솔마을 사거리</v>
+        <v>금곡동176</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>청솔마을사거리</v>
+        <v>청솔마을계룡아파트 112동 앞 도로(정자일로30)</v>
       </c>
       <c r="T46" t="str">
-        <v/>
+        <v>현장확인필요</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B47" t="str">
         <v>성남대로</v>
       </c>
       <c r="C47" t="str">
-        <v>26-성남시-06</v>
+        <v>26-성남시-07</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F47" t="str">
         <v>양호</v>
@@ -3143,7 +3143,7 @@
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>청솔마을계룡아파트 112동 앞 도로(정자일로30)</v>
+        <v>청솔마을계룡아파트 어린이놀이터 앞 도로(정자일로30)</v>
       </c>
       <c r="T47" t="str">
         <v>현장확인필요</v>
@@ -3151,19 +3151,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B48" t="str">
         <v>성남대로</v>
       </c>
       <c r="C48" t="str">
-        <v>26-성남시-07</v>
+        <v>26-성남시-08</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>종균열</v>
+        <v>종횡균열</v>
       </c>
       <c r="F48" t="str">
         <v>양호</v>
@@ -3196,16 +3196,16 @@
         <v>일반</v>
       </c>
       <c r="P48" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q48" t="str">
-        <v>금곡동176</v>
+        <v>금곡동177</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>청솔마을계룡아파트 어린이놀이터 앞 도로(정자일로30)</v>
+        <v>청솔마을서광영남아파트 101동 앞 도로(성남대로171번길8</v>
       </c>
       <c r="T48" t="str">
         <v>현장확인필요</v>
@@ -3213,19 +3213,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B49" t="str">
-        <v>성남대로</v>
+        <v>성낟매로</v>
       </c>
       <c r="C49" t="str">
-        <v>26-성남시-08</v>
+        <v>26-성남시-09</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
       </c>
       <c r="E49" t="str">
-        <v>종횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F49" t="str">
         <v>양호</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K49" t="str">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O49" t="str">
         <v>일반</v>
@@ -3261,83 +3261,21 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q49" t="str">
-        <v>금곡동177</v>
+        <v>분당구 금곡동177</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>청솔마을서광영남아파트 101동 앞 도로(성남대로171번길8</v>
+        <v>청솔마을서광영남아파트 103동 앞 도로(성남대로171번길8)</v>
       </c>
       <c r="T49" t="str">
         <v>현장확인필요</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50">
-        <v>73712</v>
-      </c>
-      <c r="B50" t="str">
-        <v>수동추가</v>
-      </c>
-      <c r="C50" t="str">
-        <v>ADD</v>
-      </c>
-      <c r="D50" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E50" t="str">
-        <v>양호</v>
-      </c>
-      <c r="F50" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G50" t="str">
-        <v>0</v>
-      </c>
-      <c r="H50" t="str">
-        <v>-</v>
-      </c>
-      <c r="I50" t="str">
-        <v/>
-      </c>
-      <c r="J50" t="str">
-        <v/>
-      </c>
-      <c r="K50" t="str">
-        <v/>
-      </c>
-      <c r="L50" t="str">
-        <v/>
-      </c>
-      <c r="M50" t="str">
-        <v/>
-      </c>
-      <c r="N50" t="str">
-        <v/>
-      </c>
-      <c r="O50" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P50" t="str">
-        <v/>
-      </c>
-      <c r="Q50" t="str">
-        <v>분당구 금곡동177</v>
-      </c>
-      <c r="R50" t="str">
-        <v/>
-      </c>
-      <c r="S50" t="str">
-        <v>직접입력</v>
-      </c>
-      <c r="T50" t="str">
-        <v>현장확인필요</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T49"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T49"/>
+  <dimension ref="A1:T50"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3216,7 +3216,7 @@
         <v>26-09</v>
       </c>
       <c r="B49" t="str">
-        <v>성낟매로</v>
+        <v>성남대로</v>
       </c>
       <c r="C49" t="str">
         <v>26-성남시-09</v>
@@ -3273,9 +3273,71 @@
         <v>현장확인필요</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>26-10</v>
+      </c>
+      <c r="B50" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C50" t="str">
+        <v>26-성남시-10</v>
+      </c>
+      <c r="D50" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E50" t="str">
+        <v>종,횡균열</v>
+      </c>
+      <c r="F50" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G50" t="str">
+        <v>0</v>
+      </c>
+      <c r="H50" t="str">
+        <v>-</v>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+      <c r="K50" t="str">
+        <v/>
+      </c>
+      <c r="L50" t="str">
+        <v/>
+      </c>
+      <c r="M50" t="str">
+        <v/>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
+        <v/>
+      </c>
+      <c r="R50" t="str">
+        <v/>
+      </c>
+      <c r="S50" t="str">
+        <v>직접입력</v>
+      </c>
+      <c r="T50" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T50"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -3075,7 +3075,7 @@
         <v>-</v>
       </c>
       <c r="Q46" t="str">
-        <v>금곡동176</v>
+        <v>분당구 금곡동176</v>
       </c>
       <c r="R46" t="str">
         <v/>
@@ -3137,7 +3137,7 @@
         <v>-</v>
       </c>
       <c r="Q47" t="str">
-        <v>금곡동176</v>
+        <v>분당구 금곡동176</v>
       </c>
       <c r="R47" t="str">
         <v/>
@@ -3199,7 +3199,7 @@
         <v>5cm이하 침하</v>
       </c>
       <c r="Q48" t="str">
-        <v>금곡동177</v>
+        <v>분당구 금곡동177</v>
       </c>
       <c r="R48" t="str">
         <v/>
@@ -3293,43 +3293,43 @@
         <v>양호</v>
       </c>
       <c r="G50" t="str">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="H50" t="str">
         <v>-</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="J50" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="L50" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="M50" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="N50" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="O50" t="str">
         <v>일반</v>
       </c>
       <c r="P50" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q50" t="str">
-        <v/>
+        <v>분당구 금곡동161</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>직접입력</v>
+        <v/>
       </c>
       <c r="T50" t="str">
         <v>현장확인필요</v>

--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -3084,7 +3084,7 @@
         <v>청솔마을계룡아파트 112동 앞 도로(정자일로30)</v>
       </c>
       <c r="T46" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="47">
@@ -3146,7 +3146,7 @@
         <v>청솔마을계룡아파트 어린이놀이터 앞 도로(정자일로30)</v>
       </c>
       <c r="T47" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="48">
@@ -3208,7 +3208,7 @@
         <v>청솔마을서광영남아파트 101동 앞 도로(성남대로171번길8</v>
       </c>
       <c r="T48" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="49">
@@ -3270,7 +3270,7 @@
         <v>청솔마을서광영남아파트 103동 앞 도로(성남대로171번길8)</v>
       </c>
       <c r="T49" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="50">
@@ -3329,10 +3329,10 @@
         <v/>
       </c>
       <c r="S50" t="str">
-        <v/>
+        <v>천사의도시1 옥된장 앞 도로(성남대로165)</v>
       </c>
       <c r="T50" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T50"/>
+  <dimension ref="A1:T51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3335,9 +3335,71 @@
         <v/>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>26-11</v>
+      </c>
+      <c r="B51" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C51" t="str">
+        <v>26-성남시-11</v>
+      </c>
+      <c r="D51" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E51" t="str">
+        <v>횡균열</v>
+      </c>
+      <c r="F51" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G51" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H51" t="str">
+        <v>-</v>
+      </c>
+      <c r="I51" t="str">
+        <v>0</v>
+      </c>
+      <c r="J51" t="str">
+        <v>1</v>
+      </c>
+      <c r="K51" t="str">
+        <v>0</v>
+      </c>
+      <c r="L51" t="str">
+        <v>1</v>
+      </c>
+      <c r="M51" t="str">
+        <v>0</v>
+      </c>
+      <c r="N51" t="str">
+        <v>2</v>
+      </c>
+      <c r="O51" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P51" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q51" t="str">
+        <v>분당구 금곡동161</v>
+      </c>
+      <c r="R51" t="str">
+        <v/>
+      </c>
+      <c r="S51" t="str">
+        <v>천사의도시1 새마을금고 앞 도로(성남대로165)</v>
+      </c>
+      <c r="T51" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T50"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:T52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3394,12 +3394,74 @@
         <v>천사의도시1 새마을금고 앞 도로(성남대로165)</v>
       </c>
       <c r="T51" t="str">
-        <v>현장확인필요</v>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>26-12</v>
+      </c>
+      <c r="B52" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C52" t="str">
+        <v>26-성남시-12</v>
+      </c>
+      <c r="D52" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E52" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F52" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G52" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H52" t="str">
+        <v>-</v>
+      </c>
+      <c r="I52" t="str">
+        <v>0</v>
+      </c>
+      <c r="J52" t="str">
+        <v>3</v>
+      </c>
+      <c r="K52" t="str">
+        <v>0</v>
+      </c>
+      <c r="L52" t="str">
+        <v>1</v>
+      </c>
+      <c r="M52" t="str">
+        <v>0</v>
+      </c>
+      <c r="N52" t="str">
+        <v>4</v>
+      </c>
+      <c r="O52" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P52" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q52" t="str">
+        <v>미금사거리</v>
+      </c>
+      <c r="R52" t="str">
+        <v/>
+      </c>
+      <c r="S52" t="str">
+        <v>미금사거리</v>
+      </c>
+      <c r="T52" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T52"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T52"/>
+  <dimension ref="A1:T53"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3287,7 +3287,7 @@
         <v>양호</v>
       </c>
       <c r="E50" t="str">
-        <v>종,횡균열</v>
+        <v>종횡균열</v>
       </c>
       <c r="F50" t="str">
         <v>양호</v>
@@ -3459,9 +3459,71 @@
         <v/>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>26-13</v>
+      </c>
+      <c r="B53" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C53" t="str">
+        <v>26-성남시-13</v>
+      </c>
+      <c r="D53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E53" t="str">
+        <v>종횡균열</v>
+      </c>
+      <c r="F53" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G53" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H53" t="str">
+        <v>-</v>
+      </c>
+      <c r="I53" t="str">
+        <v>0</v>
+      </c>
+      <c r="J53" t="str">
+        <v>1</v>
+      </c>
+      <c r="K53" t="str">
+        <v>0</v>
+      </c>
+      <c r="L53" t="str">
+        <v>1</v>
+      </c>
+      <c r="M53" t="str">
+        <v>0</v>
+      </c>
+      <c r="N53" t="str">
+        <v>2</v>
+      </c>
+      <c r="O53" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P53" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q53" t="str">
+        <v>분당구 구미동9-1</v>
+      </c>
+      <c r="R53" t="str">
+        <v/>
+      </c>
+      <c r="S53" t="str">
+        <v>분당엠코헤리츠 스타벅스 앞 도로(성남대로151)</v>
+      </c>
+      <c r="T53" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T53"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -485,19 +485,19 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="str">
         <v>성남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-성남시-3</v>
+        <v>25-성남시-4</v>
       </c>
       <c r="D5" t="str">
-        <v>보통</v>
+        <v>양호</v>
       </c>
       <c r="E5" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F5" t="str">
         <v>건조</v>
@@ -509,10 +509,10 @@
         <v>-</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -530,16 +530,16 @@
         <v>일반</v>
       </c>
       <c r="P5" t="str">
-        <v>보도침하 8cm</v>
+        <v/>
       </c>
       <c r="Q5" t="str">
-        <v>정자동 180</v>
+        <v>정자동 187-7</v>
       </c>
       <c r="R5" t="str">
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>미켈란쉐르빌 B동 앞 맞음편 보도</v>
+        <v>야생화지하보도 양차선도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="str">
         <v>성남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-성남시-4</v>
+        <v>25-성남시-5</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -601,7 +601,7 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>야생화지하보도 양차선도로</v>
+        <v>상록마을 버스정류장 앞 양차선도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,13 +609,13 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" t="str">
         <v>성남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-성남시-5</v>
+        <v>25-성남시-6</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
@@ -657,13 +657,13 @@
         <v/>
       </c>
       <c r="Q7" t="str">
-        <v>정자동 187-7</v>
+        <v>금곡사거리</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>상록마을 버스정류장 앞 양차선도로</v>
+        <v>금곡사거리 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,19 +671,19 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" t="str">
         <v>성남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-성남시-6</v>
+        <v>25-성남시-7</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
       </c>
       <c r="E8" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F8" t="str">
         <v>건조</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -710,7 +710,7 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O8" t="str">
         <v>일반</v>
@@ -719,13 +719,13 @@
         <v/>
       </c>
       <c r="Q8" t="str">
-        <v>금곡사거리</v>
+        <v>금곡동 127</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>금곡사거리 도로</v>
+        <v>분당경영고등학교 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,19 +733,19 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="str">
         <v>성남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-성남시-7</v>
+        <v>25-성남시-8</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
       </c>
       <c r="E9" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F9" t="str">
         <v>건조</v>
@@ -760,7 +760,7 @@
         <v>0</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K9">
         <v>0</v>
@@ -772,22 +772,22 @@
         <v>0</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O9" t="str">
         <v>일반</v>
       </c>
       <c r="P9" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q9" t="str">
-        <v>금곡동 127</v>
+        <v>금곡동 127-1</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>분당경영고등학교 앞 도로</v>
+        <v>#연결선 환기구 앞 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" t="str">
         <v>성남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-성남시-8</v>
+        <v>25-성남시-9</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -840,16 +840,16 @@
         <v>일반</v>
       </c>
       <c r="P10" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q10" t="str">
-        <v>금곡동 127-1</v>
+        <v>금곡동 126</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>#연결선 환기구 앞 도로</v>
+        <v>청솔주공6단지 버스정류장 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" t="str">
         <v>성남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-성남시-9</v>
+        <v>25-성남시-10</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -905,13 +905,13 @@
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v>금곡동 126</v>
+        <v>청솔마을사거리</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>청솔주공6단지 버스정류장 앞 도로</v>
+        <v>청솔마을 사거리 앞 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,13 +919,13 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" t="str">
         <v>성남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-성남시-10</v>
+        <v>25-성남시-11</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
@@ -967,13 +967,13 @@
         <v/>
       </c>
       <c r="Q12" t="str">
-        <v>청솔마을사거리</v>
+        <v>금곡동 144</v>
       </c>
       <c r="R12" t="str">
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>청솔마을 사거리 앞 도로</v>
+        <v>청솔마을성원7단지 아파트707동 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,19 +981,19 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" t="str">
         <v>성남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-성남시-11</v>
+        <v>25-성남시-12</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
       </c>
       <c r="E13" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F13" t="str">
         <v>건조</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O13" t="str">
         <v>일반</v>
@@ -1035,7 +1035,7 @@
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>청솔마을성원7단지 아파트707동 도로</v>
+        <v>청솔마을성원7단지 아파트706동 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,19 +1043,19 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="str">
         <v>성남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-성남시-12</v>
+        <v>25-성남시-13</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
       </c>
       <c r="E14" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F14" t="str">
         <v>건조</v>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="N14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O14" t="str">
         <v>일반</v>
@@ -1091,13 +1091,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>금곡동 144</v>
+        <v>금곡동 177</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>청솔마을성원7단지 아파트706동 도로</v>
+        <v>청솔마을 서광영남아파트103동 앞 도로</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,13 +1105,13 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" t="str">
         <v>성남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-성남시-13</v>
+        <v>25-성남시-14</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>금곡동 177</v>
+        <v>금곡동 159</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>청솔마을 서광영남아파트103동 앞 도로</v>
+        <v>GS25 분당성원점 앞 횡단보도</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,19 +1167,19 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" t="str">
         <v>성남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-성남시-14</v>
+        <v>25-성남시-15</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
       </c>
       <c r="E16" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F16" t="str">
         <v>건조</v>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O16" t="str">
         <v>일반</v>
@@ -1215,13 +1215,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>금곡동 159</v>
+        <v>금곡동 161</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>GS25 분당성원점 앞 횡단보도</v>
+        <v>옥된장 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,19 +1229,19 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" t="str">
         <v>성남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-성남시-15</v>
+        <v>25-성남시-16</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
       </c>
       <c r="E17" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F17" t="str">
         <v>건조</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="N17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O17" t="str">
         <v>일반</v>
@@ -1277,13 +1277,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>금곡동 161</v>
+        <v>금곡동 158</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>옥된장 앞 도로</v>
+        <v>올리브영 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" t="str">
         <v>성남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-성남시-16</v>
+        <v>25-성남시-17</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1339,13 +1339,13 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>금곡동 158</v>
+        <v>금곡동 164</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>올리브영 앞 도로</v>
+        <v>미금역 버스정류장 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" t="str">
         <v>성남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-성남시-17</v>
+        <v>25-성남시-18</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>금곡동 164</v>
+        <v>금곡동 157</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>미금역 버스정류장 앞 도로</v>
+        <v>미금역 #1번출구 앞 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,13 +1415,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" t="str">
         <v>성남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-성남시-18</v>
+        <v>25-성남시-19</v>
       </c>
       <c r="D20" t="str">
         <v>양호</v>
@@ -1463,13 +1463,13 @@
         <v/>
       </c>
       <c r="Q20" t="str">
-        <v>금곡동 157</v>
+        <v>구미동 23-1</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>미금역 #1번출구 앞 도로</v>
+        <v>미금역 교차로 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,19 +1477,19 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" t="str">
         <v>성남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-성남시-19</v>
+        <v>25-성남시-20</v>
       </c>
       <c r="D21" t="str">
-        <v>양호</v>
+        <v>보통</v>
       </c>
       <c r="E21" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F21" t="str">
         <v>건조</v>
@@ -1501,10 +1501,10 @@
         <v>-</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J21">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1516,22 +1516,22 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" t="str">
         <v>일반</v>
       </c>
       <c r="P21" t="str">
-        <v/>
+        <v>침하 5cm</v>
       </c>
       <c r="Q21" t="str">
-        <v>구미동 23-1</v>
+        <v>금곡동 157</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>미금역 교차로 도로</v>
+        <v>미금역 #2번출구 앞 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,19 +1539,19 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B22" t="str">
         <v>성남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-성남시-20</v>
+        <v>25-성남시-21</v>
       </c>
       <c r="D22" t="str">
-        <v>보통</v>
+        <v>양호</v>
       </c>
       <c r="E22" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F22" t="str">
         <v>건조</v>
@@ -1563,10 +1563,10 @@
         <v>-</v>
       </c>
       <c r="I22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1578,22 +1578,22 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O22" t="str">
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v>침하 5cm</v>
+        <v/>
       </c>
       <c r="Q22" t="str">
-        <v>금곡동 157</v>
+        <v>구미동 23-1</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>미금역 #2번출구 앞 도로</v>
+        <v>미금역 교차로 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B23" t="str">
         <v>성남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-성남시-21</v>
+        <v>25-성남시-22</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
       </c>
       <c r="E23" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F23" t="str">
         <v>건조</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1640,22 +1640,22 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O23" t="str">
         <v>일반</v>
       </c>
       <c r="P23" t="str">
-        <v/>
+        <v>침하 3cm</v>
       </c>
       <c r="Q23" t="str">
-        <v>구미동 23-1</v>
+        <v>구미동 9-1</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>미금역 교차로 도로</v>
+        <v>미금역 #5출구 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,19 +1663,19 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B24" t="str">
         <v>성남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-성남시-22</v>
+        <v>25-성남시-23</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
       </c>
       <c r="E24" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F24" t="str">
         <v>건조</v>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1702,22 +1702,22 @@
         <v>0</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O24" t="str">
         <v>일반</v>
       </c>
       <c r="P24" t="str">
-        <v>침하 3cm</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q24" t="str">
-        <v>구미동 9-1</v>
+        <v>구미동 23-4</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>미금역 #5출구 앞 도로</v>
+        <v>미금역 피난계단 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,13 +1725,13 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B25" t="str">
         <v>성남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-성남시-23</v>
+        <v>25-성남시-24</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
@@ -1770,16 +1770,16 @@
         <v>일반</v>
       </c>
       <c r="P25" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q25" t="str">
-        <v>구미동 23-4</v>
+        <v>구미동 9-1</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>미금역 피난계단 앞 도로</v>
+        <v>나무수커피 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,19 +1787,19 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="str">
         <v>성남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-성남시-24</v>
+        <v>25-성남시-25</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
       </c>
       <c r="E26" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F26" t="str">
         <v>건조</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -1826,22 +1826,22 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O26" t="str">
         <v>일반</v>
       </c>
       <c r="P26" t="str">
-        <v/>
+        <v>침하 4cm</v>
       </c>
       <c r="Q26" t="str">
-        <v>구미동 9-1</v>
+        <v>구미동 23-4</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>나무수커피 앞 도로</v>
+        <v>택시승강장 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,19 +1849,19 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B27" t="str">
         <v>성남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-성남시-25</v>
+        <v>25-성남시-26</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
       </c>
       <c r="E27" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F27" t="str">
         <v>건조</v>
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O27" t="str">
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v>침하 4cm</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q27" t="str">
-        <v>구미동 23-4</v>
+        <v>구미동 23-3</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>택시승강장 앞 도로</v>
+        <v>성남고용복지 플러스센터 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B28" t="str">
         <v>성남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-성남시-26</v>
+        <v>25-성남시-27</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1956,16 +1956,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q28" t="str">
-        <v>구미동 23-3</v>
+        <v>구미동 14-1</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>성남고용복지 플러스센터 앞 도로</v>
+        <v>까치마을 건영빌라 503동 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,13 +1973,13 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29" t="str">
         <v>성남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-성남시-27</v>
+        <v>25-성남시-28</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
@@ -2018,16 +2018,16 @@
         <v>일반</v>
       </c>
       <c r="P29" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q29" t="str">
-        <v>구미동 14-1</v>
+        <v>구미동 21-1</v>
       </c>
       <c r="R29" t="str">
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>까치마을 건영빌라 503동 앞 도로</v>
+        <v>까치마을 건영빌라 303동 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B30" t="str">
         <v>성남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-성남시-28</v>
+        <v>25-성남시-29</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
       </c>
       <c r="E30" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F30" t="str">
         <v>건조</v>
@@ -2061,8 +2061,8 @@
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30">
-        <v>3</v>
+      <c r="J30" t="b">
+        <v>0</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -2074,7 +2074,7 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O30" t="str">
         <v>일반</v>
@@ -2089,7 +2089,7 @@
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>까치마을 건영빌라 303동 앞 도로</v>
+        <v>까치마을 건영빌라 302동 앞 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,19 +2097,19 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="str">
         <v>성남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-성남시-29</v>
+        <v>25-성남시-30</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
       </c>
       <c r="E31" t="str">
-        <v>양호</v>
+        <v>횡균열</v>
       </c>
       <c r="F31" t="str">
         <v>건조</v>
@@ -2123,8 +2123,8 @@
       <c r="I31">
         <v>0</v>
       </c>
-      <c r="J31" t="b">
-        <v>0</v>
+      <c r="J31">
+        <v>1</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -2136,13 +2136,13 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O31" t="str">
         <v>일반</v>
       </c>
       <c r="P31" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q31" t="str">
         <v>구미동 21-1</v>
@@ -2151,7 +2151,7 @@
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>까치마을 건영빌라 302동 앞 도로</v>
+        <v>까치마을 지하보도 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,19 +2159,19 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B32" t="str">
         <v>성남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-성남시-30</v>
+        <v>25-성남시-31</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
       </c>
       <c r="E32" t="str">
-        <v>횡균열</v>
+        <v>-</v>
       </c>
       <c r="F32" t="str">
         <v>건조</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2198,22 +2198,22 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O32" t="str">
         <v>일반</v>
       </c>
       <c r="P32" t="str">
-        <v/>
+        <v>침하 2cm</v>
       </c>
       <c r="Q32" t="str">
-        <v>구미동 21-1</v>
+        <v>구미동 13</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>까치마을 지하보도 도로</v>
+        <v>까치마을 건영빌라 603동 앞 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,19 +2221,19 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" t="str">
         <v>성남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-성남시-31</v>
+        <v>25-성남시-32</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
       </c>
       <c r="E33" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F33" t="str">
         <v>건조</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -2260,22 +2260,22 @@
         <v>0</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O33" t="str">
         <v>일반</v>
       </c>
       <c r="P33" t="str">
-        <v>침하 2cm</v>
+        <v/>
       </c>
       <c r="Q33" t="str">
-        <v>구미동 13</v>
+        <v>미금사거리</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>까치마을 건영빌라 603동 앞 도로</v>
+        <v>미금사거리 도로</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,13 +2283,13 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" t="str">
         <v>성남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-성남시-32</v>
+        <v>25-성남시-33</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
@@ -2331,13 +2331,13 @@
         <v/>
       </c>
       <c r="Q34" t="str">
-        <v>미금사거리</v>
+        <v>구미동 17</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>미금사거리 도로</v>
+        <v>성남구미도서관 앞 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,13 +2345,13 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" t="str">
         <v>성남대로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-성남시-33</v>
+        <v>25-성남시-34</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
@@ -2390,16 +2390,16 @@
         <v>일반</v>
       </c>
       <c r="P35" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q35" t="str">
-        <v>구미동 17</v>
+        <v>구미동 149-1</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>성남구미도서관 앞 도로</v>
+        <v>서울그린빌 1동 앞 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,13 +2407,13 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>성남대로</v>
+        <v>탄천상로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-성남시-34</v>
+        <v>25-성남시-35</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
@@ -2452,16 +2452,16 @@
         <v>일반</v>
       </c>
       <c r="P36" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q36" t="str">
-        <v>구미동 149-1</v>
+        <v>구미동 170-2</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>서울그린빌 1동 앞 도로</v>
+        <v>동막교 앞 사거리 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,13 +2469,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B37" t="str">
         <v>탄천상로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-성남시-35</v>
+        <v>25-성남시-36</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2517,13 +2517,13 @@
         <v/>
       </c>
       <c r="Q37" t="str">
-        <v>구미동 170-2</v>
+        <v>구미동 170-1</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>동막교 앞 사거리 도로</v>
+        <v>KD운송그룹 분당영업소 앞 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>탄천상로</v>
+        <v>분당수서로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-성남시-36</v>
+        <v>25-성남시-37</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>구미동 170-1</v>
+        <v>경기고속삼거리</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>KD운송그룹 분당영업소 앞 도로</v>
+        <v>경기고속 삼거리 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>분당수서로</v>
+        <v>신수로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-성남시-37</v>
+        <v>25-성남시-38</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2641,27 +2641,27 @@
         <v/>
       </c>
       <c r="Q39" t="str">
-        <v>경기고속삼거리</v>
+        <v>구미동 824-4</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>경기고속 삼거리 도로</v>
+        <v>강원철물건재 앞 도로</v>
       </c>
       <c r="T39" t="str">
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>38</v>
+      <c r="A40" t="str">
+        <v>26-01</v>
       </c>
       <c r="B40" t="str">
-        <v>신수로</v>
+        <v>성남대로</v>
       </c>
       <c r="C40" t="str">
-        <v>25-성남시-38</v>
+        <v>26-성남시-01</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
@@ -2670,46 +2670,46 @@
         <v>거북등</v>
       </c>
       <c r="F40" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G40" t="str">
-        <v>9.3</v>
+        <v>10.3</v>
       </c>
       <c r="H40" t="str">
         <v>-</v>
       </c>
-      <c r="I40">
-        <v>0</v>
-      </c>
-      <c r="J40">
-        <v>3</v>
-      </c>
-      <c r="K40">
-        <v>0</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>0</v>
-      </c>
-      <c r="N40">
-        <v>3</v>
+      <c r="I40" t="str">
+        <v>0</v>
+      </c>
+      <c r="J40" t="str">
+        <v>3</v>
+      </c>
+      <c r="K40" t="str">
+        <v>0</v>
+      </c>
+      <c r="L40" t="str">
+        <v>1</v>
+      </c>
+      <c r="M40" t="str">
+        <v>0</v>
+      </c>
+      <c r="N40" t="str">
+        <v>4</v>
       </c>
       <c r="O40" t="str">
         <v>일반</v>
       </c>
       <c r="P40" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q40" t="str">
-        <v>구미동 824-4</v>
+        <v>정자동180</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>강원철물건재 앞 도로</v>
+        <v>미켈란쉐르빌아파트 앞 양차선(정자일로100)</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,19 +2717,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B41" t="str">
         <v>성남대로</v>
       </c>
       <c r="C41" t="str">
-        <v>26-성남시-01</v>
+        <v>26-성남시-02</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
       </c>
       <c r="E41" t="str">
-        <v>거북등</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F41" t="str">
         <v>양호</v>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="J41" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K41" t="str">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O41" t="str">
         <v>일반</v>
@@ -2765,13 +2765,13 @@
         <v>-</v>
       </c>
       <c r="Q41" t="str">
-        <v>정자동180</v>
+        <v>정자동181</v>
       </c>
       <c r="R41" t="str">
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>미켈란쉐르빌아파트 앞 양차선(정자일로100)</v>
+        <v>상록마을 임광보성아파트 406동 앞 도로(정자일로80)</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,19 +2779,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B42" t="str">
         <v>성남대로</v>
       </c>
       <c r="C42" t="str">
-        <v>26-성남시-02</v>
+        <v>26-성남시-03</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
       </c>
       <c r="E42" t="str">
-        <v>종,횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F42" t="str">
         <v>양호</v>
@@ -2824,7 +2824,7 @@
         <v>일반</v>
       </c>
       <c r="P42" t="str">
-        <v>-</v>
+        <v>5cm이하 침하(바퀴자리)</v>
       </c>
       <c r="Q42" t="str">
         <v>정자동181</v>
@@ -2833,7 +2833,7 @@
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>상록마을 임광보성아파트 406동 앞 도로(정자일로80)</v>
+        <v>상록마을 임광보성아파트 408동 앞 도로(정자일로80)</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,19 +2841,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B43" t="str">
         <v>성남대로</v>
       </c>
       <c r="C43" t="str">
-        <v>26-성남시-03</v>
+        <v>26-성남시-04</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
       </c>
       <c r="E43" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F43" t="str">
         <v>양호</v>
@@ -2868,7 +2868,7 @@
         <v>0</v>
       </c>
       <c r="J43" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K43" t="str">
         <v>0</v>
@@ -2880,22 +2880,22 @@
         <v>0</v>
       </c>
       <c r="N43" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O43" t="str">
         <v>일반</v>
       </c>
       <c r="P43" t="str">
-        <v>5cm이하 침하(바퀴자리)</v>
+        <v>-</v>
       </c>
       <c r="Q43" t="str">
-        <v>정자동181</v>
+        <v>금곡사거리</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>상록마을 임광보성아파트 408동 앞 도로(정자일로80)</v>
+        <v>금곡사거리</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,13 +2903,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B44" t="str">
         <v>성남대로</v>
       </c>
       <c r="C44" t="str">
-        <v>26-성남시-04</v>
+        <v>26-성남시-05</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
@@ -2951,13 +2951,13 @@
         <v>-</v>
       </c>
       <c r="Q44" t="str">
-        <v>금곡사거리</v>
+        <v>청솔마을 사거리</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>금곡사거리</v>
+        <v>청솔마을사거리</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,19 +2965,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B45" t="str">
         <v>성남대로</v>
       </c>
       <c r="C45" t="str">
-        <v>26-성남시-05</v>
+        <v>26-성남시-06</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
       </c>
       <c r="E45" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F45" t="str">
         <v>양호</v>
@@ -2992,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K45" t="str">
         <v>0</v>
@@ -3004,7 +3004,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O45" t="str">
         <v>일반</v>
@@ -3013,13 +3013,13 @@
         <v>-</v>
       </c>
       <c r="Q45" t="str">
-        <v>청솔마을 사거리</v>
+        <v>분당구 금곡동176</v>
       </c>
       <c r="R45" t="str">
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>청솔마을사거리</v>
+        <v>청솔마을계룡아파트 112동 앞 도로(정자일로30)</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,19 +3027,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B46" t="str">
         <v>성남대로</v>
       </c>
       <c r="C46" t="str">
-        <v>26-성남시-06</v>
+        <v>26-성남시-07</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
       </c>
       <c r="E46" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F46" t="str">
         <v>양호</v>
@@ -3081,7 +3081,7 @@
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>청솔마을계룡아파트 112동 앞 도로(정자일로30)</v>
+        <v>청솔마을계룡아파트 어린이놀이터 앞 도로(정자일로30)</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3089,19 +3089,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B47" t="str">
         <v>성남대로</v>
       </c>
       <c r="C47" t="str">
-        <v>26-성남시-07</v>
+        <v>26-성남시-08</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>종균열</v>
+        <v>종횡균열</v>
       </c>
       <c r="F47" t="str">
         <v>양호</v>
@@ -3134,16 +3134,16 @@
         <v>일반</v>
       </c>
       <c r="P47" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q47" t="str">
-        <v>분당구 금곡동176</v>
+        <v>분당구 금곡동177</v>
       </c>
       <c r="R47" t="str">
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>청솔마을계룡아파트 어린이놀이터 앞 도로(정자일로30)</v>
+        <v>청솔마을서광영남아파트 101동 앞 도로(성남대로171번길8</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3151,19 +3151,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B48" t="str">
         <v>성남대로</v>
       </c>
       <c r="C48" t="str">
-        <v>26-성남시-08</v>
+        <v>26-성남시-09</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>종횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F48" t="str">
         <v>양호</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K48" t="str">
         <v>0</v>
@@ -3190,7 +3190,7 @@
         <v>0</v>
       </c>
       <c r="N48" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O48" t="str">
         <v>일반</v>
@@ -3205,7 +3205,7 @@
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>청솔마을서광영남아파트 101동 앞 도로(성남대로171번길8</v>
+        <v>청솔마을서광영남아파트 103동 앞 도로(성남대로171번길8)</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B49" t="str">
         <v>성남대로</v>
       </c>
       <c r="C49" t="str">
-        <v>26-성남시-09</v>
+        <v>26-성남시-10</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
       </c>
       <c r="E49" t="str">
-        <v>거북등</v>
+        <v>종횡균열</v>
       </c>
       <c r="F49" t="str">
         <v>양호</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="J49" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K49" t="str">
         <v>0</v>
@@ -3252,22 +3252,22 @@
         <v>0</v>
       </c>
       <c r="N49" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O49" t="str">
         <v>일반</v>
       </c>
       <c r="P49" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q49" t="str">
-        <v>분당구 금곡동177</v>
+        <v>분당구 금곡동161</v>
       </c>
       <c r="R49" t="str">
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>청솔마을서광영남아파트 103동 앞 도로(성남대로171번길8)</v>
+        <v>천사의도시1 옥된장 앞 도로(성남대로165)</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3275,19 +3275,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B50" t="str">
         <v>성남대로</v>
       </c>
       <c r="C50" t="str">
-        <v>26-성남시-10</v>
+        <v>26-성남시-11</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
       </c>
       <c r="E50" t="str">
-        <v>종횡균열</v>
+        <v>횡균열</v>
       </c>
       <c r="F50" t="str">
         <v>양호</v>
@@ -3329,7 +3329,7 @@
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>천사의도시1 옥된장 앞 도로(성남대로165)</v>
+        <v>천사의도시1 새마을금고 앞 도로(성남대로165)</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3337,19 +3337,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B51" t="str">
         <v>성남대로</v>
       </c>
       <c r="C51" t="str">
-        <v>26-성남시-11</v>
+        <v>26-성남시-12</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
       </c>
       <c r="E51" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F51" t="str">
         <v>양호</v>
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K51" t="str">
         <v>0</v>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O51" t="str">
         <v>일반</v>
@@ -3385,13 +3385,13 @@
         <v>-</v>
       </c>
       <c r="Q51" t="str">
-        <v>분당구 금곡동161</v>
+        <v>미금사거리</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>천사의도시1 새마을금고 앞 도로(성남대로165)</v>
+        <v>미금사거리</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3399,19 +3399,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B52" t="str">
         <v>성남대로</v>
       </c>
       <c r="C52" t="str">
-        <v>26-성남시-12</v>
+        <v>26-성남시-13</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
       </c>
       <c r="E52" t="str">
-        <v>거북등</v>
+        <v>종횡균열</v>
       </c>
       <c r="F52" t="str">
         <v>양호</v>
@@ -3426,7 +3426,7 @@
         <v>0</v>
       </c>
       <c r="J52" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K52" t="str">
         <v>0</v>
@@ -3438,7 +3438,7 @@
         <v>0</v>
       </c>
       <c r="N52" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O52" t="str">
         <v>일반</v>
@@ -3447,13 +3447,13 @@
         <v>-</v>
       </c>
       <c r="Q52" t="str">
-        <v>미금사거리</v>
+        <v>분당구 구미동9-1</v>
       </c>
       <c r="R52" t="str">
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>미금사거리</v>
+        <v>분당엠코헤리츠 스타벅스 앞 도로(성남대로151)</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3461,13 +3461,13 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B53" t="str">
         <v>성남대로</v>
       </c>
       <c r="C53" t="str">
-        <v>26-성남시-13</v>
+        <v>26-성남시-14</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
@@ -3515,10 +3515,10 @@
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>분당엠코헤리츠 스타벅스 앞 도로(성남대로151)</v>
+        <v>분당엠코헤리츠 나무수커피 앞 도로(성남대로151)</v>
       </c>
       <c r="T53" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T53"/>
+  <dimension ref="A1:T56"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3521,9 +3521,195 @@
         <v/>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>26-15</v>
+      </c>
+      <c r="B54" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C54" t="str">
+        <v>26-성남시-15</v>
+      </c>
+      <c r="D54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E54" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F54" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G54" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H54" t="str">
+        <v>-</v>
+      </c>
+      <c r="I54" t="str">
+        <v>0</v>
+      </c>
+      <c r="J54" t="str">
+        <v>3</v>
+      </c>
+      <c r="K54" t="str">
+        <v>0</v>
+      </c>
+      <c r="L54" t="str">
+        <v>1</v>
+      </c>
+      <c r="M54" t="str">
+        <v>0</v>
+      </c>
+      <c r="N54" t="str">
+        <v>4</v>
+      </c>
+      <c r="O54" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P54" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q54" t="str">
+        <v>분당구 구미동14-1</v>
+      </c>
+      <c r="R54" t="str">
+        <v/>
+      </c>
+      <c r="S54" t="str">
+        <v>까치마을 건영빌라 505동 앞 도로(미금일로136)</v>
+      </c>
+      <c r="T54" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>26-16</v>
+      </c>
+      <c r="B55" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C55" t="str">
+        <v>26-성남시-16</v>
+      </c>
+      <c r="D55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E55" t="str">
+        <v>종균열</v>
+      </c>
+      <c r="F55" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G55" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H55" t="str">
+        <v>-</v>
+      </c>
+      <c r="I55" t="str">
+        <v>0</v>
+      </c>
+      <c r="J55" t="str">
+        <v>1</v>
+      </c>
+      <c r="K55" t="str">
+        <v>0</v>
+      </c>
+      <c r="L55" t="str">
+        <v>1</v>
+      </c>
+      <c r="M55" t="str">
+        <v>0</v>
+      </c>
+      <c r="N55" t="str">
+        <v>2</v>
+      </c>
+      <c r="O55" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P55" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q55" t="str">
+        <v>분당구 구미동13</v>
+      </c>
+      <c r="R55" t="str">
+        <v/>
+      </c>
+      <c r="S55" t="str">
+        <v>까치마을 건영빌라 604동 앞 도로(미금일로122)</v>
+      </c>
+      <c r="T55" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>26-17</v>
+      </c>
+      <c r="B56" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C56" t="str">
+        <v>26-성남시-17</v>
+      </c>
+      <c r="D56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="F56" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G56" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H56" t="str">
+        <v>-</v>
+      </c>
+      <c r="I56" t="str">
+        <v>0</v>
+      </c>
+      <c r="J56" t="str">
+        <v>0</v>
+      </c>
+      <c r="K56" t="str">
+        <v>0</v>
+      </c>
+      <c r="L56" t="str">
+        <v>1</v>
+      </c>
+      <c r="M56" t="str">
+        <v>0</v>
+      </c>
+      <c r="N56" t="str">
+        <v>1</v>
+      </c>
+      <c r="O56" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P56" t="str">
+        <v>5cm이하 침하(바퀴자리)</v>
+      </c>
+      <c r="Q56" t="str">
+        <v>분당구 구미동13</v>
+      </c>
+      <c r="R56" t="str">
+        <v/>
+      </c>
+      <c r="S56" t="str">
+        <v>까치마을 건영빌라 609동 앞 횡단보도(미금일로122)</v>
+      </c>
+      <c r="T56" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T53"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T56"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T58"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3707,9 +3707,133 @@
         <v>현장확인필요</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>26-18</v>
+      </c>
+      <c r="B57" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C57" t="str">
+        <v>26-성남시-18</v>
+      </c>
+      <c r="D57" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E57" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F57" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G57" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H57" t="str">
+        <v>-</v>
+      </c>
+      <c r="I57" t="str">
+        <v>0</v>
+      </c>
+      <c r="J57" t="str">
+        <v>3</v>
+      </c>
+      <c r="K57" t="str">
+        <v>0</v>
+      </c>
+      <c r="L57" t="str">
+        <v>1</v>
+      </c>
+      <c r="M57" t="str">
+        <v>0</v>
+      </c>
+      <c r="N57" t="str">
+        <v>4</v>
+      </c>
+      <c r="O57" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P57" t="str">
+        <v>5cm이하 침하</v>
+      </c>
+      <c r="Q57" t="str">
+        <v>분당구 구미동17</v>
+      </c>
+      <c r="R57" t="str">
+        <v/>
+      </c>
+      <c r="S57" t="str">
+        <v>구미도서관 앞 양차선(미금일로101)</v>
+      </c>
+      <c r="T57" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>26-19</v>
+      </c>
+      <c r="B58" t="str">
+        <v>성남대로</v>
+      </c>
+      <c r="C58" t="str">
+        <v>26-성남시-19</v>
+      </c>
+      <c r="D58" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E58" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F58" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G58" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H58" t="str">
+        <v>-</v>
+      </c>
+      <c r="I58" t="str">
+        <v>0</v>
+      </c>
+      <c r="J58" t="str">
+        <v>3</v>
+      </c>
+      <c r="K58" t="str">
+        <v>0</v>
+      </c>
+      <c r="L58" t="str">
+        <v>1</v>
+      </c>
+      <c r="M58" t="str">
+        <v>0</v>
+      </c>
+      <c r="N58" t="str">
+        <v>4</v>
+      </c>
+      <c r="O58" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P58" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q58" t="str">
+        <v>분당구 구미동148</v>
+      </c>
+      <c r="R58" t="str">
+        <v/>
+      </c>
+      <c r="S58" t="str">
+        <v>성지빌라 앞 양차선(금곡로7번길7)</v>
+      </c>
+      <c r="T58" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T56"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T58"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T58"/>
+  <dimension ref="A1:T59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3831,9 +3831,71 @@
         <v>현장확인필요</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>26-20</v>
+      </c>
+      <c r="B59" t="str">
+        <v>분당수서로</v>
+      </c>
+      <c r="C59" t="str">
+        <v>26-성남시-20</v>
+      </c>
+      <c r="D59" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E59" t="str">
+        <v>거북등</v>
+      </c>
+      <c r="F59" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G59" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H59" t="str">
+        <v>-</v>
+      </c>
+      <c r="I59" t="str">
+        <v>0</v>
+      </c>
+      <c r="J59" t="str">
+        <v>3</v>
+      </c>
+      <c r="K59" t="str">
+        <v>0</v>
+      </c>
+      <c r="L59" t="str">
+        <v>1</v>
+      </c>
+      <c r="M59" t="str">
+        <v>0</v>
+      </c>
+      <c r="N59" t="str">
+        <v>4</v>
+      </c>
+      <c r="O59" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P59" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q59" t="str">
+        <v>경기고속삼거리</v>
+      </c>
+      <c r="R59" t="str">
+        <v/>
+      </c>
+      <c r="S59" t="str">
+        <v>경기고속삼거리(탄천상로171)</v>
+      </c>
+      <c r="T59" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T59"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T59"/>
+  <dimension ref="A1:T60"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3893,9 +3893,71 @@
         <v>현장확인필요</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>26-21</v>
+      </c>
+      <c r="B60" t="str">
+        <v>대왕판교로</v>
+      </c>
+      <c r="C60" t="str">
+        <v>26-성남시-21</v>
+      </c>
+      <c r="D60" t="str">
+        <v>양호</v>
+      </c>
+      <c r="E60" t="str">
+        <v>종횡균열</v>
+      </c>
+      <c r="F60" t="str">
+        <v>양호</v>
+      </c>
+      <c r="G60" t="str">
+        <v>10.3</v>
+      </c>
+      <c r="H60" t="str">
+        <v>-</v>
+      </c>
+      <c r="I60" t="str">
+        <v>0</v>
+      </c>
+      <c r="J60" t="str">
+        <v>1</v>
+      </c>
+      <c r="K60" t="str">
+        <v>0</v>
+      </c>
+      <c r="L60" t="str">
+        <v>1</v>
+      </c>
+      <c r="M60" t="str">
+        <v>0</v>
+      </c>
+      <c r="N60" t="str">
+        <v>2</v>
+      </c>
+      <c r="O60" t="str">
+        <v>일반</v>
+      </c>
+      <c r="P60" t="str">
+        <v>-</v>
+      </c>
+      <c r="Q60" t="str">
+        <v>분당구 구미동824-4</v>
+      </c>
+      <c r="R60" t="str">
+        <v/>
+      </c>
+      <c r="S60" t="str">
+        <v>강원철물건재 앞 도로(신수로787)</v>
+      </c>
+      <c r="T60" t="str">
+        <v>현장확인필요</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T60"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/25-경기철도-성남시-보고서.xlsx
+++ b/25-경기철도-성남시-보고서.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:T59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,13 +485,13 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" t="str">
         <v>성남대로</v>
       </c>
       <c r="C5" t="str">
-        <v>25-성남시-4</v>
+        <v>25-성남시-5</v>
       </c>
       <c r="D5" t="str">
         <v>양호</v>
@@ -539,7 +539,7 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>야생화지하보도 양차선도로</v>
+        <v>상록마을 버스정류장 앞 양차선도로</v>
       </c>
       <c r="T5" t="str">
         <v/>
@@ -547,13 +547,13 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="str">
         <v>성남대로</v>
       </c>
       <c r="C6" t="str">
-        <v>25-성남시-5</v>
+        <v>25-성남시-6</v>
       </c>
       <c r="D6" t="str">
         <v>양호</v>
@@ -595,13 +595,13 @@
         <v/>
       </c>
       <c r="Q6" t="str">
-        <v>정자동 187-7</v>
+        <v>금곡사거리</v>
       </c>
       <c r="R6" t="str">
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>상록마을 버스정류장 앞 양차선도로</v>
+        <v>금곡사거리 도로</v>
       </c>
       <c r="T6" t="str">
         <v/>
@@ -609,19 +609,19 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="str">
         <v>성남대로</v>
       </c>
       <c r="C7" t="str">
-        <v>25-성남시-6</v>
+        <v>25-성남시-7</v>
       </c>
       <c r="D7" t="str">
         <v>양호</v>
       </c>
       <c r="E7" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F7" t="str">
         <v>건조</v>
@@ -636,7 +636,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="N7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O7" t="str">
         <v>일반</v>
@@ -657,13 +657,13 @@
         <v/>
       </c>
       <c r="Q7" t="str">
-        <v>금곡사거리</v>
+        <v>금곡동 127</v>
       </c>
       <c r="R7" t="str">
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>금곡사거리 도로</v>
+        <v>분당경영고등학교 앞 도로</v>
       </c>
       <c r="T7" t="str">
         <v/>
@@ -671,19 +671,19 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="str">
         <v>성남대로</v>
       </c>
       <c r="C8" t="str">
-        <v>25-성남시-7</v>
+        <v>25-성남시-8</v>
       </c>
       <c r="D8" t="str">
         <v>양호</v>
       </c>
       <c r="E8" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F8" t="str">
         <v>건조</v>
@@ -698,7 +698,7 @@
         <v>0</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K8">
         <v>0</v>
@@ -710,22 +710,22 @@
         <v>0</v>
       </c>
       <c r="N8">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O8" t="str">
         <v>일반</v>
       </c>
       <c r="P8" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q8" t="str">
-        <v>금곡동 127</v>
+        <v>금곡동 127-1</v>
       </c>
       <c r="R8" t="str">
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>분당경영고등학교 앞 도로</v>
+        <v>#연결선 환기구 앞 도로</v>
       </c>
       <c r="T8" t="str">
         <v/>
@@ -733,13 +733,13 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="str">
         <v>성남대로</v>
       </c>
       <c r="C9" t="str">
-        <v>25-성남시-8</v>
+        <v>25-성남시-9</v>
       </c>
       <c r="D9" t="str">
         <v>양호</v>
@@ -778,16 +778,16 @@
         <v>일반</v>
       </c>
       <c r="P9" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q9" t="str">
-        <v>금곡동 127-1</v>
+        <v>금곡동 126</v>
       </c>
       <c r="R9" t="str">
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>#연결선 환기구 앞 도로</v>
+        <v>청솔주공6단지 버스정류장 앞 도로</v>
       </c>
       <c r="T9" t="str">
         <v/>
@@ -795,13 +795,13 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="str">
         <v>성남대로</v>
       </c>
       <c r="C10" t="str">
-        <v>25-성남시-9</v>
+        <v>25-성남시-10</v>
       </c>
       <c r="D10" t="str">
         <v>양호</v>
@@ -843,13 +843,13 @@
         <v/>
       </c>
       <c r="Q10" t="str">
-        <v>금곡동 126</v>
+        <v>청솔마을사거리</v>
       </c>
       <c r="R10" t="str">
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>청솔주공6단지 버스정류장 앞 도로</v>
+        <v>청솔마을 사거리 앞 도로</v>
       </c>
       <c r="T10" t="str">
         <v/>
@@ -857,13 +857,13 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="str">
         <v>성남대로</v>
       </c>
       <c r="C11" t="str">
-        <v>25-성남시-10</v>
+        <v>25-성남시-11</v>
       </c>
       <c r="D11" t="str">
         <v>양호</v>
@@ -905,13 +905,13 @@
         <v/>
       </c>
       <c r="Q11" t="str">
-        <v>청솔마을사거리</v>
+        <v>금곡동 144</v>
       </c>
       <c r="R11" t="str">
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>청솔마을 사거리 앞 도로</v>
+        <v>청솔마을성원7단지 아파트707동 도로</v>
       </c>
       <c r="T11" t="str">
         <v/>
@@ -919,19 +919,19 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="str">
         <v>성남대로</v>
       </c>
       <c r="C12" t="str">
-        <v>25-성남시-11</v>
+        <v>25-성남시-12</v>
       </c>
       <c r="D12" t="str">
         <v>양호</v>
       </c>
       <c r="E12" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F12" t="str">
         <v>건조</v>
@@ -946,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K12">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O12" t="str">
         <v>일반</v>
@@ -973,7 +973,7 @@
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>청솔마을성원7단지 아파트707동 도로</v>
+        <v>청솔마을성원7단지 아파트706동 도로</v>
       </c>
       <c r="T12" t="str">
         <v/>
@@ -981,19 +981,19 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="str">
         <v>성남대로</v>
       </c>
       <c r="C13" t="str">
-        <v>25-성남시-12</v>
+        <v>25-성남시-13</v>
       </c>
       <c r="D13" t="str">
         <v>양호</v>
       </c>
       <c r="E13" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F13" t="str">
         <v>건조</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -1020,7 +1020,7 @@
         <v>0</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O13" t="str">
         <v>일반</v>
@@ -1029,13 +1029,13 @@
         <v/>
       </c>
       <c r="Q13" t="str">
-        <v>금곡동 144</v>
+        <v>금곡동 177</v>
       </c>
       <c r="R13" t="str">
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>청솔마을성원7단지 아파트706동 도로</v>
+        <v>청솔마을 서광영남아파트103동 앞 도로</v>
       </c>
       <c r="T13" t="str">
         <v/>
@@ -1043,13 +1043,13 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="str">
         <v>성남대로</v>
       </c>
       <c r="C14" t="str">
-        <v>25-성남시-13</v>
+        <v>25-성남시-14</v>
       </c>
       <c r="D14" t="str">
         <v>양호</v>
@@ -1091,13 +1091,13 @@
         <v/>
       </c>
       <c r="Q14" t="str">
-        <v>금곡동 177</v>
+        <v>금곡동 159</v>
       </c>
       <c r="R14" t="str">
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>청솔마을 서광영남아파트103동 앞 도로</v>
+        <v>GS25 분당성원점 앞 횡단보도</v>
       </c>
       <c r="T14" t="str">
         <v/>
@@ -1105,19 +1105,19 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="str">
         <v>성남대로</v>
       </c>
       <c r="C15" t="str">
-        <v>25-성남시-14</v>
+        <v>25-성남시-15</v>
       </c>
       <c r="D15" t="str">
         <v>양호</v>
       </c>
       <c r="E15" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F15" t="str">
         <v>건조</v>
@@ -1132,7 +1132,7 @@
         <v>0</v>
       </c>
       <c r="J15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -1144,7 +1144,7 @@
         <v>0</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O15" t="str">
         <v>일반</v>
@@ -1153,13 +1153,13 @@
         <v/>
       </c>
       <c r="Q15" t="str">
-        <v>금곡동 159</v>
+        <v>금곡동 161</v>
       </c>
       <c r="R15" t="str">
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>GS25 분당성원점 앞 횡단보도</v>
+        <v>옥된장 앞 도로</v>
       </c>
       <c r="T15" t="str">
         <v/>
@@ -1167,19 +1167,19 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="str">
         <v>성남대로</v>
       </c>
       <c r="C16" t="str">
-        <v>25-성남시-15</v>
+        <v>25-성남시-16</v>
       </c>
       <c r="D16" t="str">
         <v>양호</v>
       </c>
       <c r="E16" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F16" t="str">
         <v>건조</v>
@@ -1194,7 +1194,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -1206,7 +1206,7 @@
         <v>0</v>
       </c>
       <c r="N16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O16" t="str">
         <v>일반</v>
@@ -1215,13 +1215,13 @@
         <v/>
       </c>
       <c r="Q16" t="str">
-        <v>금곡동 161</v>
+        <v>금곡동 158</v>
       </c>
       <c r="R16" t="str">
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>옥된장 앞 도로</v>
+        <v>올리브영 앞 도로</v>
       </c>
       <c r="T16" t="str">
         <v/>
@@ -1229,13 +1229,13 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="str">
         <v>성남대로</v>
       </c>
       <c r="C17" t="str">
-        <v>25-성남시-16</v>
+        <v>25-성남시-17</v>
       </c>
       <c r="D17" t="str">
         <v>양호</v>
@@ -1277,13 +1277,13 @@
         <v/>
       </c>
       <c r="Q17" t="str">
-        <v>금곡동 158</v>
+        <v>금곡동 164</v>
       </c>
       <c r="R17" t="str">
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>올리브영 앞 도로</v>
+        <v>미금역 버스정류장 앞 도로</v>
       </c>
       <c r="T17" t="str">
         <v/>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B18" t="str">
         <v>성남대로</v>
       </c>
       <c r="C18" t="str">
-        <v>25-성남시-17</v>
+        <v>25-성남시-18</v>
       </c>
       <c r="D18" t="str">
         <v>양호</v>
@@ -1339,13 +1339,13 @@
         <v/>
       </c>
       <c r="Q18" t="str">
-        <v>금곡동 164</v>
+        <v>금곡동 157</v>
       </c>
       <c r="R18" t="str">
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>미금역 버스정류장 앞 도로</v>
+        <v>미금역 #1번출구 앞 도로</v>
       </c>
       <c r="T18" t="str">
         <v/>
@@ -1353,13 +1353,13 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="str">
         <v>성남대로</v>
       </c>
       <c r="C19" t="str">
-        <v>25-성남시-18</v>
+        <v>25-성남시-19</v>
       </c>
       <c r="D19" t="str">
         <v>양호</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="Q19" t="str">
-        <v>금곡동 157</v>
+        <v>구미동 23-1</v>
       </c>
       <c r="R19" t="str">
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>미금역 #1번출구 앞 도로</v>
+        <v>미금역 교차로 도로</v>
       </c>
       <c r="T19" t="str">
         <v/>
@@ -1415,19 +1415,19 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B20" t="str">
         <v>성남대로</v>
       </c>
       <c r="C20" t="str">
-        <v>25-성남시-19</v>
+        <v>25-성남시-20</v>
       </c>
       <c r="D20" t="str">
-        <v>양호</v>
+        <v>보통</v>
       </c>
       <c r="E20" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F20" t="str">
         <v>건조</v>
@@ -1439,10 +1439,10 @@
         <v>-</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -1454,22 +1454,22 @@
         <v>0</v>
       </c>
       <c r="N20">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20" t="str">
         <v>일반</v>
       </c>
       <c r="P20" t="str">
-        <v/>
+        <v>침하 5cm</v>
       </c>
       <c r="Q20" t="str">
-        <v>구미동 23-1</v>
+        <v>금곡동 157</v>
       </c>
       <c r="R20" t="str">
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>미금역 교차로 도로</v>
+        <v>미금역 #2번출구 앞 도로</v>
       </c>
       <c r="T20" t="str">
         <v/>
@@ -1477,19 +1477,19 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B21" t="str">
         <v>성남대로</v>
       </c>
       <c r="C21" t="str">
-        <v>25-성남시-20</v>
+        <v>25-성남시-21</v>
       </c>
       <c r="D21" t="str">
-        <v>보통</v>
+        <v>양호</v>
       </c>
       <c r="E21" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F21" t="str">
         <v>건조</v>
@@ -1501,10 +1501,10 @@
         <v>-</v>
       </c>
       <c r="I21">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -1516,22 +1516,22 @@
         <v>0</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O21" t="str">
         <v>일반</v>
       </c>
       <c r="P21" t="str">
-        <v>침하 5cm</v>
+        <v/>
       </c>
       <c r="Q21" t="str">
-        <v>금곡동 157</v>
+        <v>구미동 23-1</v>
       </c>
       <c r="R21" t="str">
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>미금역 #2번출구 앞 도로</v>
+        <v>미금역 교차로 도로</v>
       </c>
       <c r="T21" t="str">
         <v/>
@@ -1539,19 +1539,19 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B22" t="str">
         <v>성남대로</v>
       </c>
       <c r="C22" t="str">
-        <v>25-성남시-21</v>
+        <v>25-성남시-22</v>
       </c>
       <c r="D22" t="str">
         <v>양호</v>
       </c>
       <c r="E22" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F22" t="str">
         <v>건조</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="J22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -1578,22 +1578,22 @@
         <v>0</v>
       </c>
       <c r="N22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O22" t="str">
         <v>일반</v>
       </c>
       <c r="P22" t="str">
-        <v/>
+        <v>침하 3cm</v>
       </c>
       <c r="Q22" t="str">
-        <v>구미동 23-1</v>
+        <v>구미동 9-1</v>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>미금역 교차로 도로</v>
+        <v>미금역 #5출구 앞 도로</v>
       </c>
       <c r="T22" t="str">
         <v/>
@@ -1601,19 +1601,19 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B23" t="str">
         <v>성남대로</v>
       </c>
       <c r="C23" t="str">
-        <v>25-성남시-22</v>
+        <v>25-성남시-23</v>
       </c>
       <c r="D23" t="str">
         <v>양호</v>
       </c>
       <c r="E23" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F23" t="str">
         <v>건조</v>
@@ -1628,7 +1628,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1640,22 +1640,22 @@
         <v>0</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O23" t="str">
         <v>일반</v>
       </c>
       <c r="P23" t="str">
-        <v>침하 3cm</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q23" t="str">
-        <v>구미동 9-1</v>
+        <v>구미동 23-4</v>
       </c>
       <c r="R23" t="str">
         <v/>
       </c>
       <c r="S23" t="str">
-        <v>미금역 #5출구 앞 도로</v>
+        <v>미금역 피난계단 앞 도로</v>
       </c>
       <c r="T23" t="str">
         <v/>
@@ -1663,13 +1663,13 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B24" t="str">
         <v>성남대로</v>
       </c>
       <c r="C24" t="str">
-        <v>25-성남시-23</v>
+        <v>25-성남시-24</v>
       </c>
       <c r="D24" t="str">
         <v>양호</v>
@@ -1708,16 +1708,16 @@
         <v>일반</v>
       </c>
       <c r="P24" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q24" t="str">
-        <v>구미동 23-4</v>
+        <v>구미동 9-1</v>
       </c>
       <c r="R24" t="str">
         <v/>
       </c>
       <c r="S24" t="str">
-        <v>미금역 피난계단 앞 도로</v>
+        <v>나무수커피 앞 도로</v>
       </c>
       <c r="T24" t="str">
         <v/>
@@ -1725,19 +1725,19 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B25" t="str">
         <v>성남대로</v>
       </c>
       <c r="C25" t="str">
-        <v>25-성남시-24</v>
+        <v>25-성남시-25</v>
       </c>
       <c r="D25" t="str">
         <v>양호</v>
       </c>
       <c r="E25" t="str">
-        <v>거북등</v>
+        <v>-</v>
       </c>
       <c r="F25" t="str">
         <v>건조</v>
@@ -1752,7 +1752,7 @@
         <v>0</v>
       </c>
       <c r="J25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -1764,22 +1764,22 @@
         <v>0</v>
       </c>
       <c r="N25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="str">
         <v>일반</v>
       </c>
       <c r="P25" t="str">
-        <v/>
+        <v>침하 4cm</v>
       </c>
       <c r="Q25" t="str">
-        <v>구미동 9-1</v>
+        <v>구미동 23-4</v>
       </c>
       <c r="R25" t="str">
         <v/>
       </c>
       <c r="S25" t="str">
-        <v>나무수커피 앞 도로</v>
+        <v>택시승강장 앞 도로</v>
       </c>
       <c r="T25" t="str">
         <v/>
@@ -1787,19 +1787,19 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B26" t="str">
         <v>성남대로</v>
       </c>
       <c r="C26" t="str">
-        <v>25-성남시-25</v>
+        <v>25-성남시-26</v>
       </c>
       <c r="D26" t="str">
         <v>양호</v>
       </c>
       <c r="E26" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F26" t="str">
         <v>건조</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K26">
         <v>0</v>
@@ -1826,22 +1826,22 @@
         <v>0</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O26" t="str">
         <v>일반</v>
       </c>
       <c r="P26" t="str">
-        <v>침하 4cm</v>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q26" t="str">
-        <v>구미동 23-4</v>
+        <v>구미동 23-3</v>
       </c>
       <c r="R26" t="str">
         <v/>
       </c>
       <c r="S26" t="str">
-        <v>택시승강장 앞 도로</v>
+        <v>성남고용복지 플러스센터 앞 도로</v>
       </c>
       <c r="T26" t="str">
         <v/>
@@ -1849,13 +1849,13 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27" t="str">
         <v>성남대로</v>
       </c>
       <c r="C27" t="str">
-        <v>25-성남시-26</v>
+        <v>25-성남시-27</v>
       </c>
       <c r="D27" t="str">
         <v>양호</v>
@@ -1894,16 +1894,16 @@
         <v>일반</v>
       </c>
       <c r="P27" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q27" t="str">
-        <v>구미동 23-3</v>
+        <v>구미동 14-1</v>
       </c>
       <c r="R27" t="str">
         <v/>
       </c>
       <c r="S27" t="str">
-        <v>성남고용복지 플러스센터 앞 도로</v>
+        <v>까치마을 건영빌라 503동 앞 도로</v>
       </c>
       <c r="T27" t="str">
         <v/>
@@ -1911,13 +1911,13 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28" t="str">
         <v>성남대로</v>
       </c>
       <c r="C28" t="str">
-        <v>25-성남시-27</v>
+        <v>25-성남시-28</v>
       </c>
       <c r="D28" t="str">
         <v>양호</v>
@@ -1956,16 +1956,16 @@
         <v>일반</v>
       </c>
       <c r="P28" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q28" t="str">
-        <v>구미동 14-1</v>
+        <v>구미동 21-1</v>
       </c>
       <c r="R28" t="str">
         <v/>
       </c>
       <c r="S28" t="str">
-        <v>까치마을 건영빌라 503동 앞 도로</v>
+        <v>까치마을 건영빌라 303동 앞 도로</v>
       </c>
       <c r="T28" t="str">
         <v/>
@@ -1973,19 +1973,19 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B29" t="str">
         <v>성남대로</v>
       </c>
       <c r="C29" t="str">
-        <v>25-성남시-28</v>
+        <v>25-성남시-29</v>
       </c>
       <c r="D29" t="str">
         <v>양호</v>
       </c>
       <c r="E29" t="str">
-        <v>거북등</v>
+        <v>양호</v>
       </c>
       <c r="F29" t="str">
         <v>건조</v>
@@ -1999,8 +1999,8 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="J29">
-        <v>3</v>
+      <c r="J29" t="b">
+        <v>0</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -2012,7 +2012,7 @@
         <v>0</v>
       </c>
       <c r="N29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O29" t="str">
         <v>일반</v>
@@ -2027,7 +2027,7 @@
         <v/>
       </c>
       <c r="S29" t="str">
-        <v>까치마을 건영빌라 303동 앞 도로</v>
+        <v>까치마을 건영빌라 302동 앞 도로</v>
       </c>
       <c r="T29" t="str">
         <v/>
@@ -2035,19 +2035,19 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B30" t="str">
         <v>성남대로</v>
       </c>
       <c r="C30" t="str">
-        <v>25-성남시-29</v>
+        <v>25-성남시-30</v>
       </c>
       <c r="D30" t="str">
         <v>양호</v>
       </c>
       <c r="E30" t="str">
-        <v>양호</v>
+        <v>횡균열</v>
       </c>
       <c r="F30" t="str">
         <v>건조</v>
@@ -2061,8 +2061,8 @@
       <c r="I30">
         <v>0</v>
       </c>
-      <c r="J30" t="b">
-        <v>0</v>
+      <c r="J30">
+        <v>1</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O30" t="str">
         <v>일반</v>
       </c>
       <c r="P30" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q30" t="str">
         <v>구미동 21-1</v>
@@ -2089,7 +2089,7 @@
         <v/>
       </c>
       <c r="S30" t="str">
-        <v>까치마을 건영빌라 302동 앞 도로</v>
+        <v>까치마을 지하보도 도로</v>
       </c>
       <c r="T30" t="str">
         <v/>
@@ -2097,19 +2097,19 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B31" t="str">
         <v>성남대로</v>
       </c>
       <c r="C31" t="str">
-        <v>25-성남시-30</v>
+        <v>25-성남시-31</v>
       </c>
       <c r="D31" t="str">
         <v>양호</v>
       </c>
       <c r="E31" t="str">
-        <v>횡균열</v>
+        <v>-</v>
       </c>
       <c r="F31" t="str">
         <v>건조</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="J31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -2136,22 +2136,22 @@
         <v>0</v>
       </c>
       <c r="N31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O31" t="str">
         <v>일반</v>
       </c>
       <c r="P31" t="str">
-        <v/>
+        <v>침하 2cm</v>
       </c>
       <c r="Q31" t="str">
-        <v>구미동 21-1</v>
+        <v>구미동 13</v>
       </c>
       <c r="R31" t="str">
         <v/>
       </c>
       <c r="S31" t="str">
-        <v>까치마을 지하보도 도로</v>
+        <v>까치마을 건영빌라 603동 앞 도로</v>
       </c>
       <c r="T31" t="str">
         <v/>
@@ -2159,19 +2159,19 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" t="str">
         <v>성남대로</v>
       </c>
       <c r="C32" t="str">
-        <v>25-성남시-31</v>
+        <v>25-성남시-32</v>
       </c>
       <c r="D32" t="str">
         <v>양호</v>
       </c>
       <c r="E32" t="str">
-        <v>-</v>
+        <v>거북등</v>
       </c>
       <c r="F32" t="str">
         <v>건조</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -2198,22 +2198,22 @@
         <v>0</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O32" t="str">
         <v>일반</v>
       </c>
       <c r="P32" t="str">
-        <v>침하 2cm</v>
+        <v/>
       </c>
       <c r="Q32" t="str">
-        <v>구미동 13</v>
+        <v>미금사거리</v>
       </c>
       <c r="R32" t="str">
         <v/>
       </c>
       <c r="S32" t="str">
-        <v>까치마을 건영빌라 603동 앞 도로</v>
+        <v>미금사거리 도로</v>
       </c>
       <c r="T32" t="str">
         <v/>
@@ -2221,13 +2221,13 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" t="str">
         <v>성남대로</v>
       </c>
       <c r="C33" t="str">
-        <v>25-성남시-32</v>
+        <v>25-성남시-33</v>
       </c>
       <c r="D33" t="str">
         <v>양호</v>
@@ -2269,13 +2269,13 @@
         <v/>
       </c>
       <c r="Q33" t="str">
-        <v>미금사거리</v>
+        <v>구미동 17</v>
       </c>
       <c r="R33" t="str">
         <v/>
       </c>
       <c r="S33" t="str">
-        <v>미금사거리 도로</v>
+        <v>성남구미도서관 앞 도로</v>
       </c>
       <c r="T33" t="str">
         <v/>
@@ -2283,13 +2283,13 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" t="str">
         <v>성남대로</v>
       </c>
       <c r="C34" t="str">
-        <v>25-성남시-33</v>
+        <v>25-성남시-34</v>
       </c>
       <c r="D34" t="str">
         <v>양호</v>
@@ -2328,16 +2328,16 @@
         <v>일반</v>
       </c>
       <c r="P34" t="str">
-        <v/>
+        <v>5cm미만 침하</v>
       </c>
       <c r="Q34" t="str">
-        <v>구미동 17</v>
+        <v>구미동 149-1</v>
       </c>
       <c r="R34" t="str">
         <v/>
       </c>
       <c r="S34" t="str">
-        <v>성남구미도서관 앞 도로</v>
+        <v>서울그린빌 1동 앞 도로</v>
       </c>
       <c r="T34" t="str">
         <v/>
@@ -2345,13 +2345,13 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" t="str">
-        <v>성남대로</v>
+        <v>탄천상로</v>
       </c>
       <c r="C35" t="str">
-        <v>25-성남시-34</v>
+        <v>25-성남시-35</v>
       </c>
       <c r="D35" t="str">
         <v>양호</v>
@@ -2390,16 +2390,16 @@
         <v>일반</v>
       </c>
       <c r="P35" t="str">
-        <v>5cm미만 침하</v>
+        <v/>
       </c>
       <c r="Q35" t="str">
-        <v>구미동 149-1</v>
+        <v>구미동 170-2</v>
       </c>
       <c r="R35" t="str">
         <v/>
       </c>
       <c r="S35" t="str">
-        <v>서울그린빌 1동 앞 도로</v>
+        <v>동막교 앞 사거리 도로</v>
       </c>
       <c r="T35" t="str">
         <v/>
@@ -2407,13 +2407,13 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" t="str">
         <v>탄천상로</v>
       </c>
       <c r="C36" t="str">
-        <v>25-성남시-35</v>
+        <v>25-성남시-36</v>
       </c>
       <c r="D36" t="str">
         <v>양호</v>
@@ -2455,13 +2455,13 @@
         <v/>
       </c>
       <c r="Q36" t="str">
-        <v>구미동 170-2</v>
+        <v>구미동 170-1</v>
       </c>
       <c r="R36" t="str">
         <v/>
       </c>
       <c r="S36" t="str">
-        <v>동막교 앞 사거리 도로</v>
+        <v>KD운송그룹 분당영업소 앞 도로</v>
       </c>
       <c r="T36" t="str">
         <v/>
@@ -2469,13 +2469,13 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" t="str">
-        <v>탄천상로</v>
+        <v>분당수서로</v>
       </c>
       <c r="C37" t="str">
-        <v>25-성남시-36</v>
+        <v>25-성남시-37</v>
       </c>
       <c r="D37" t="str">
         <v>양호</v>
@@ -2517,13 +2517,13 @@
         <v/>
       </c>
       <c r="Q37" t="str">
-        <v>구미동 170-1</v>
+        <v>경기고속삼거리</v>
       </c>
       <c r="R37" t="str">
         <v/>
       </c>
       <c r="S37" t="str">
-        <v>KD운송그룹 분당영업소 앞 도로</v>
+        <v>경기고속 삼거리 도로</v>
       </c>
       <c r="T37" t="str">
         <v/>
@@ -2531,13 +2531,13 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" t="str">
-        <v>분당수서로</v>
+        <v>신수로</v>
       </c>
       <c r="C38" t="str">
-        <v>25-성남시-37</v>
+        <v>25-성남시-38</v>
       </c>
       <c r="D38" t="str">
         <v>양호</v>
@@ -2579,27 +2579,27 @@
         <v/>
       </c>
       <c r="Q38" t="str">
-        <v>경기고속삼거리</v>
+        <v>구미동 824-4</v>
       </c>
       <c r="R38" t="str">
         <v/>
       </c>
       <c r="S38" t="str">
-        <v>경기고속 삼거리 도로</v>
+        <v>강원철물건재 앞 도로</v>
       </c>
       <c r="T38" t="str">
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>26-01</v>
       </c>
       <c r="B39" t="str">
-        <v>신수로</v>
+        <v>성남대로</v>
       </c>
       <c r="C39" t="str">
-        <v>25-성남시-38</v>
+        <v>26-성남시-01</v>
       </c>
       <c r="D39" t="str">
         <v>양호</v>
@@ -2608,46 +2608,46 @@
         <v>거북등</v>
       </c>
       <c r="F39" t="str">
-        <v>건조</v>
+        <v>양호</v>
       </c>
       <c r="G39" t="str">
-        <v>9.3</v>
+        <v>10.3</v>
       </c>
       <c r="H39" t="str">
         <v>-</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>3</v>
-      </c>
-      <c r="K39">
-        <v>0</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>0</v>
-      </c>
-      <c r="N39">
-        <v>3</v>
+      <c r="I39" t="str">
+        <v>0</v>
+      </c>
+      <c r="J39" t="str">
+        <v>3</v>
+      </c>
+      <c r="K39" t="str">
+        <v>0</v>
+      </c>
+      <c r="L39" t="str">
+        <v>1</v>
+      </c>
+      <c r="M39" t="str">
+        <v>0</v>
+      </c>
+      <c r="N39" t="str">
+        <v>4</v>
       </c>
       <c r="O39" t="str">
         <v>일반</v>
       </c>
       <c r="P39" t="str">
-        <v/>
+        <v>-</v>
       </c>
       <c r="Q39" t="str">
-        <v>구미동 824-4</v>
+        <v>정자동180</v>
       </c>
       <c r="R39" t="str">
         <v/>
       </c>
       <c r="S39" t="str">
-        <v>강원철물건재 앞 도로</v>
+        <v>미켈란쉐르빌아파트 앞 양차선(정자일로100)</v>
       </c>
       <c r="T39" t="str">
         <v/>
@@ -2655,19 +2655,19 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>26-01</v>
+        <v>26-02</v>
       </c>
       <c r="B40" t="str">
         <v>성남대로</v>
       </c>
       <c r="C40" t="str">
-        <v>26-성남시-01</v>
+        <v>26-성남시-02</v>
       </c>
       <c r="D40" t="str">
         <v>양호</v>
       </c>
       <c r="E40" t="str">
-        <v>거북등</v>
+        <v>종,횡균열</v>
       </c>
       <c r="F40" t="str">
         <v>양호</v>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K40" t="str">
         <v>0</v>
@@ -2694,7 +2694,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O40" t="str">
         <v>일반</v>
@@ -2703,13 +2703,13 @@
         <v>-</v>
       </c>
       <c r="Q40" t="str">
-        <v>정자동180</v>
+        <v>정자동181</v>
       </c>
       <c r="R40" t="str">
         <v/>
       </c>
       <c r="S40" t="str">
-        <v>미켈란쉐르빌아파트 앞 양차선(정자일로100)</v>
+        <v>상록마을 임광보성아파트 406동 앞 도로(정자일로80)</v>
       </c>
       <c r="T40" t="str">
         <v/>
@@ -2717,19 +2717,19 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>26-02</v>
+        <v>26-03</v>
       </c>
       <c r="B41" t="str">
         <v>성남대로</v>
       </c>
       <c r="C41" t="str">
-        <v>26-성남시-02</v>
+        <v>26-성남시-03</v>
       </c>
       <c r="D41" t="str">
         <v>양호</v>
       </c>
       <c r="E41" t="str">
-        <v>종,횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F41" t="str">
         <v>양호</v>
@@ -2762,7 +2762,7 @@
         <v>일반</v>
       </c>
       <c r="P41" t="str">
-        <v>-</v>
+        <v>5cm이하 침하(바퀴자리)</v>
       </c>
       <c r="Q41" t="str">
         <v>정자동181</v>
@@ -2771,7 +2771,7 @@
         <v/>
       </c>
       <c r="S41" t="str">
-        <v>상록마을 임광보성아파트 406동 앞 도로(정자일로80)</v>
+        <v>상록마을 임광보성아파트 408동 앞 도로(정자일로80)</v>
       </c>
       <c r="T41" t="str">
         <v/>
@@ -2779,19 +2779,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>26-03</v>
+        <v>26-04</v>
       </c>
       <c r="B42" t="str">
         <v>성남대로</v>
       </c>
       <c r="C42" t="str">
-        <v>26-성남시-03</v>
+        <v>26-성남시-04</v>
       </c>
       <c r="D42" t="str">
         <v>양호</v>
       </c>
       <c r="E42" t="str">
-        <v>종균열</v>
+        <v>거북등</v>
       </c>
       <c r="F42" t="str">
         <v>양호</v>
@@ -2806,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="J42" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K42" t="str">
         <v>0</v>
@@ -2818,22 +2818,22 @@
         <v>0</v>
       </c>
       <c r="N42" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O42" t="str">
         <v>일반</v>
       </c>
       <c r="P42" t="str">
-        <v>5cm이하 침하(바퀴자리)</v>
+        <v>-</v>
       </c>
       <c r="Q42" t="str">
-        <v>정자동181</v>
+        <v>금곡사거리</v>
       </c>
       <c r="R42" t="str">
         <v/>
       </c>
       <c r="S42" t="str">
-        <v>상록마을 임광보성아파트 408동 앞 도로(정자일로80)</v>
+        <v>금곡사거리</v>
       </c>
       <c r="T42" t="str">
         <v/>
@@ -2841,13 +2841,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>26-04</v>
+        <v>26-05</v>
       </c>
       <c r="B43" t="str">
         <v>성남대로</v>
       </c>
       <c r="C43" t="str">
-        <v>26-성남시-04</v>
+        <v>26-성남시-05</v>
       </c>
       <c r="D43" t="str">
         <v>양호</v>
@@ -2889,13 +2889,13 @@
         <v>-</v>
       </c>
       <c r="Q43" t="str">
-        <v>금곡사거리</v>
+        <v>청솔마을 사거리</v>
       </c>
       <c r="R43" t="str">
         <v/>
       </c>
       <c r="S43" t="str">
-        <v>금곡사거리</v>
+        <v>청솔마을사거리</v>
       </c>
       <c r="T43" t="str">
         <v/>
@@ -2903,19 +2903,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>26-05</v>
+        <v>26-06</v>
       </c>
       <c r="B44" t="str">
         <v>성남대로</v>
       </c>
       <c r="C44" t="str">
-        <v>26-성남시-05</v>
+        <v>26-성남시-06</v>
       </c>
       <c r="D44" t="str">
         <v>양호</v>
       </c>
       <c r="E44" t="str">
-        <v>거북등</v>
+        <v>횡균열</v>
       </c>
       <c r="F44" t="str">
         <v>양호</v>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="J44" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K44" t="str">
         <v>0</v>
@@ -2942,7 +2942,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O44" t="str">
         <v>일반</v>
@@ -2951,13 +2951,13 @@
         <v>-</v>
       </c>
       <c r="Q44" t="str">
-        <v>청솔마을 사거리</v>
+        <v>분당구 금곡동176</v>
       </c>
       <c r="R44" t="str">
         <v/>
       </c>
       <c r="S44" t="str">
-        <v>청솔마을사거리</v>
+        <v>청솔마을계룡아파트 112동 앞 도로(정자일로30)</v>
       </c>
       <c r="T44" t="str">
         <v/>
@@ -2965,19 +2965,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>26-06</v>
+        <v>26-07</v>
       </c>
       <c r="B45" t="str">
         <v>성남대로</v>
       </c>
       <c r="C45" t="str">
-        <v>26-성남시-06</v>
+        <v>26-성남시-07</v>
       </c>
       <c r="D45" t="str">
         <v>양호</v>
       </c>
       <c r="E45" t="str">
-        <v>횡균열</v>
+        <v>종균열</v>
       </c>
       <c r="F45" t="str">
         <v>양호</v>
@@ -3019,7 +3019,7 @@
         <v/>
       </c>
       <c r="S45" t="str">
-        <v>청솔마을계룡아파트 112동 앞 도로(정자일로30)</v>
+        <v>청솔마을계룡아파트 어린이놀이터 앞 도로(정자일로30)</v>
       </c>
       <c r="T45" t="str">
         <v/>
@@ -3027,19 +3027,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>26-07</v>
+        <v>26-08</v>
       </c>
       <c r="B46" t="str">
         <v>성남대로</v>
       </c>
       <c r="C46" t="str">
-        <v>26-성남시-07</v>
+        <v>26-성남시-08</v>
       </c>
       <c r="D46" t="str">
         <v>양호</v>
       </c>
       <c r="E46" t="str">
-        <v>종균열</v>
+        <v>종횡균열</v>
       </c>
       <c r="F46" t="str">
         <v>양호</v>
@@ -3072,16 +3072,16 @@
         <v>일반</v>
       </c>
       <c r="P46" t="str">
-        <v>-</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q46" t="str">
-        <v>분당구 금곡동176</v>
+        <v>분당구 금곡동177</v>
       </c>
       <c r="R46" t="str">
         <v/>
       </c>
       <c r="S46" t="str">
-        <v>청솔마을계룡아파트 어린이놀이터 앞 도로(정자일로30)</v>
+        <v>청솔마을서광영남아파트 101동 앞 도로(성남대로171번길8</v>
       </c>
       <c r="T46" t="str">
         <v/>
@@ -3089,19 +3089,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>26-08</v>
+        <v>26-09</v>
       </c>
       <c r="B47" t="str">
         <v>성남대로</v>
       </c>
       <c r="C47" t="str">
-        <v>26-성남시-08</v>
+        <v>26-성남시-09</v>
       </c>
       <c r="D47" t="str">
         <v>양호</v>
       </c>
       <c r="E47" t="str">
-        <v>종횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F47" t="str">
         <v>양호</v>
@@ -3116,7 +3116,7 @@
         <v>0</v>
       </c>
       <c r="J47" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K47" t="str">
         <v>0</v>
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="N47" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O47" t="str">
         <v>일반</v>
@@ -3143,7 +3143,7 @@
         <v/>
       </c>
       <c r="S47" t="str">
-        <v>청솔마을서광영남아파트 101동 앞 도로(성남대로171번길8</v>
+        <v>청솔마을서광영남아파트 103동 앞 도로(성남대로171번길8)</v>
       </c>
       <c r="T47" t="str">
         <v/>
@@ -3151,19 +3151,19 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>26-09</v>
+        <v>26-10</v>
       </c>
       <c r="B48" t="str">
         <v>성남대로</v>
       </c>
       <c r="C48" t="str">
-        <v>26-성남시-09</v>
+        <v>26-성남시-10</v>
       </c>
       <c r="D48" t="str">
         <v>양호</v>
       </c>
       <c r="E48" t="str">
-        <v>거북등</v>
+        <v>종횡균열</v>
       </c>
       <c r="F48" t="str">
         <v>양호</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="J48" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K48" t="str">
         <v>0</v>
@@ -3190,22 +3190,22 @@
         <v>0</v>
       </c>
       <c r="N48" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O48" t="str">
         <v>일반</v>
       </c>
       <c r="P48" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q48" t="str">
-        <v>분당구 금곡동177</v>
+        <v>분당구 금곡동161</v>
       </c>
       <c r="R48" t="str">
         <v/>
       </c>
       <c r="S48" t="str">
-        <v>청솔마을서광영남아파트 103동 앞 도로(성남대로171번길8)</v>
+        <v>천사의도시1 옥된장 앞 도로(성남대로165)</v>
       </c>
       <c r="T48" t="str">
         <v/>
@@ -3213,19 +3213,19 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>26-10</v>
+        <v>26-11</v>
       </c>
       <c r="B49" t="str">
         <v>성남대로</v>
       </c>
       <c r="C49" t="str">
-        <v>26-성남시-10</v>
+        <v>26-성남시-11</v>
       </c>
       <c r="D49" t="str">
         <v>양호</v>
       </c>
       <c r="E49" t="str">
-        <v>종횡균열</v>
+        <v>횡균열</v>
       </c>
       <c r="F49" t="str">
         <v>양호</v>
@@ -3267,7 +3267,7 @@
         <v/>
       </c>
       <c r="S49" t="str">
-        <v>천사의도시1 옥된장 앞 도로(성남대로165)</v>
+        <v>천사의도시1 새마을금고 앞 도로(성남대로165)</v>
       </c>
       <c r="T49" t="str">
         <v/>
@@ -3275,19 +3275,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>26-11</v>
+        <v>26-12</v>
       </c>
       <c r="B50" t="str">
         <v>성남대로</v>
       </c>
       <c r="C50" t="str">
-        <v>26-성남시-11</v>
+        <v>26-성남시-12</v>
       </c>
       <c r="D50" t="str">
         <v>양호</v>
       </c>
       <c r="E50" t="str">
-        <v>횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F50" t="str">
         <v>양호</v>
@@ -3302,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="J50" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K50" t="str">
         <v>0</v>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="N50" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O50" t="str">
         <v>일반</v>
@@ -3323,13 +3323,13 @@
         <v>-</v>
       </c>
       <c r="Q50" t="str">
-        <v>분당구 금곡동161</v>
+        <v>미금사거리</v>
       </c>
       <c r="R50" t="str">
         <v/>
       </c>
       <c r="S50" t="str">
-        <v>천사의도시1 새마을금고 앞 도로(성남대로165)</v>
+        <v>미금사거리</v>
       </c>
       <c r="T50" t="str">
         <v/>
@@ -3337,19 +3337,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>26-12</v>
+        <v>26-13</v>
       </c>
       <c r="B51" t="str">
         <v>성남대로</v>
       </c>
       <c r="C51" t="str">
-        <v>26-성남시-12</v>
+        <v>26-성남시-13</v>
       </c>
       <c r="D51" t="str">
         <v>양호</v>
       </c>
       <c r="E51" t="str">
-        <v>거북등</v>
+        <v>종횡균열</v>
       </c>
       <c r="F51" t="str">
         <v>양호</v>
@@ -3364,7 +3364,7 @@
         <v>0</v>
       </c>
       <c r="J51" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K51" t="str">
         <v>0</v>
@@ -3376,7 +3376,7 @@
         <v>0</v>
       </c>
       <c r="N51" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O51" t="str">
         <v>일반</v>
@@ -3385,13 +3385,13 @@
         <v>-</v>
       </c>
       <c r="Q51" t="str">
-        <v>미금사거리</v>
+        <v>분당구 구미동9-1</v>
       </c>
       <c r="R51" t="str">
         <v/>
       </c>
       <c r="S51" t="str">
-        <v>미금사거리</v>
+        <v>분당엠코헤리츠 스타벅스 앞 도로(성남대로151)</v>
       </c>
       <c r="T51" t="str">
         <v/>
@@ -3399,13 +3399,13 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>26-13</v>
+        <v>26-14</v>
       </c>
       <c r="B52" t="str">
         <v>성남대로</v>
       </c>
       <c r="C52" t="str">
-        <v>26-성남시-13</v>
+        <v>26-성남시-14</v>
       </c>
       <c r="D52" t="str">
         <v>양호</v>
@@ -3453,7 +3453,7 @@
         <v/>
       </c>
       <c r="S52" t="str">
-        <v>분당엠코헤리츠 스타벅스 앞 도로(성남대로151)</v>
+        <v>분당엠코헤리츠 나무수커피 앞 도로(성남대로151)</v>
       </c>
       <c r="T52" t="str">
         <v/>
@@ -3461,19 +3461,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>26-14</v>
+        <v>26-15</v>
       </c>
       <c r="B53" t="str">
         <v>성남대로</v>
       </c>
       <c r="C53" t="str">
-        <v>26-성남시-14</v>
+        <v>26-성남시-15</v>
       </c>
       <c r="D53" t="str">
         <v>양호</v>
       </c>
       <c r="E53" t="str">
-        <v>종횡균열</v>
+        <v>거북등</v>
       </c>
       <c r="F53" t="str">
         <v>양호</v>
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="J53" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K53" t="str">
         <v>0</v>
@@ -3500,7 +3500,7 @@
         <v>0</v>
       </c>
       <c r="N53" t="str">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O53" t="str">
         <v>일반</v>
@@ -3509,13 +3509,13 @@
         <v>-</v>
       </c>
       <c r="Q53" t="str">
-        <v>분당구 구미동9-1</v>
+        <v>분당구 구미동14-1</v>
       </c>
       <c r="R53" t="str">
         <v/>
       </c>
       <c r="S53" t="str">
-        <v>분당엠코헤리츠 나무수커피 앞 도로(성남대로151)</v>
+        <v>까치마을 건영빌라 505동 앞 도로(미금일로136)</v>
       </c>
       <c r="T53" t="str">
         <v/>
@@ -3523,19 +3523,19 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>26-15</v>
+        <v>26-16</v>
       </c>
       <c r="B54" t="str">
         <v>성남대로</v>
       </c>
       <c r="C54" t="str">
-        <v>26-성남시-15</v>
+        <v>26-성남시-16</v>
       </c>
       <c r="D54" t="str">
         <v>양호</v>
       </c>
       <c r="E54" t="str">
-        <v>거북등</v>
+        <v>종균열</v>
       </c>
       <c r="F54" t="str">
         <v>양호</v>
@@ -3550,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K54" t="str">
         <v>0</v>
@@ -3562,7 +3562,7 @@
         <v>0</v>
       </c>
       <c r="N54" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O54" t="str">
         <v>일반</v>
@@ -3571,33 +3571,33 @@
         <v>-</v>
       </c>
       <c r="Q54" t="str">
-        <v>분당구 구미동14-1</v>
+        <v>분당구 구미동13</v>
       </c>
       <c r="R54" t="str">
         <v/>
       </c>
       <c r="S54" t="str">
-        <v>까치마을 건영빌라 505동 앞 도로(미금일로136)</v>
+        <v>까치마을 건영빌라 604동 앞 도로(미금일로122)</v>
       </c>
       <c r="T54" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>26-16</v>
+        <v>26-17</v>
       </c>
       <c r="B55" t="str">
         <v>성남대로</v>
       </c>
       <c r="C55" t="str">
-        <v>26-성남시-16</v>
+        <v>26-성남시-17</v>
       </c>
       <c r="D55" t="str">
         <v>양호</v>
       </c>
       <c r="E55" t="str">
-        <v>종균열</v>
+        <v>양호</v>
       </c>
       <c r="F55" t="str">
         <v>양호</v>
@@ -3612,7 +3612,7 @@
         <v>0</v>
       </c>
       <c r="J55" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="str">
         <v>0</v>
@@ -3624,13 +3624,13 @@
         <v>0</v>
       </c>
       <c r="N55" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55" t="str">
         <v>일반</v>
       </c>
       <c r="P55" t="str">
-        <v>-</v>
+        <v>5cm이하 침하(바퀴자리)</v>
       </c>
       <c r="Q55" t="str">
         <v>분당구 구미동13</v>
@@ -3639,27 +3639,27 @@
         <v/>
       </c>
       <c r="S55" t="str">
-        <v>까치마을 건영빌라 604동 앞 도로(미금일로122)</v>
+        <v>까치마을 건영빌라 609동 앞 횡단보도(미금일로122)</v>
       </c>
       <c r="T55" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>26-17</v>
+        <v>26-18</v>
       </c>
       <c r="B56" t="str">
         <v>성남대로</v>
       </c>
       <c r="C56" t="str">
-        <v>26-성남시-17</v>
+        <v>26-성남시-18</v>
       </c>
       <c r="D56" t="str">
         <v>양호</v>
       </c>
       <c r="E56" t="str">
-        <v>양호</v>
+        <v>거북등</v>
       </c>
       <c r="F56" t="str">
         <v>양호</v>
@@ -3674,7 +3674,7 @@
         <v>0</v>
       </c>
       <c r="J56" t="str">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K56" t="str">
         <v>0</v>
@@ -3686,36 +3686,36 @@
         <v>0</v>
       </c>
       <c r="N56" t="str">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O56" t="str">
         <v>일반</v>
       </c>
       <c r="P56" t="str">
-        <v>5cm이하 침하(바퀴자리)</v>
+        <v>5cm이하 침하</v>
       </c>
       <c r="Q56" t="str">
-        <v>분당구 구미동13</v>
+        <v>분당구 구미동17</v>
       </c>
       <c r="R56" t="str">
         <v/>
       </c>
       <c r="S56" t="str">
-        <v>까치마을 건영빌라 609동 앞 횡단보도(미금일로122)</v>
+        <v>구미도서관 앞 양차선(미금일로101)</v>
       </c>
       <c r="T56" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>26-18</v>
+        <v>26-19</v>
       </c>
       <c r="B57" t="str">
         <v>성남대로</v>
       </c>
       <c r="C57" t="str">
-        <v>26-성남시-18</v>
+        <v>26-성남시-19</v>
       </c>
       <c r="D57" t="str">
         <v>양호</v>
@@ -3754,30 +3754,30 @@
         <v>일반</v>
       </c>
       <c r="P57" t="str">
-        <v>5cm이하 침하</v>
+        <v>-</v>
       </c>
       <c r="Q57" t="str">
-        <v>분당구 구미동17</v>
+        <v>분당구 구미동148</v>
       </c>
       <c r="R57" t="str">
         <v/>
       </c>
       <c r="S57" t="str">
-        <v>구미도서관 앞 양차선(미금일로101)</v>
+        <v>성지빌라 앞 양차선(금곡로7번길7)</v>
       </c>
       <c r="T57" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>26-19</v>
+        <v>26-20</v>
       </c>
       <c r="B58" t="str">
-        <v>성남대로</v>
+        <v>분당수서로</v>
       </c>
       <c r="C58" t="str">
-        <v>26-성남시-19</v>
+        <v>26-성남시-20</v>
       </c>
       <c r="D58" t="str">
         <v>양호</v>
@@ -3819,33 +3819,33 @@
         <v>-</v>
       </c>
       <c r="Q58" t="str">
-        <v>분당구 구미동148</v>
+        <v>경기고속삼거리</v>
       </c>
       <c r="R58" t="str">
         <v/>
       </c>
       <c r="S58" t="str">
-        <v>성지빌라 앞 양차선(금곡로7번길7)</v>
+        <v>경기고속삼거리(탄천상로171)</v>
       </c>
       <c r="T58" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>26-20</v>
+        <v>26-21</v>
       </c>
       <c r="B59" t="str">
-        <v>분당수서로</v>
+        <v>대왕판교로</v>
       </c>
       <c r="C59" t="str">
-        <v>26-성남시-20</v>
+        <v>26-성남시-21</v>
       </c>
       <c r="D59" t="str">
         <v>양호</v>
       </c>
       <c r="E59" t="str">
-        <v>거북등</v>
+        <v>종횡균열</v>
       </c>
       <c r="F59" t="str">
         <v>양호</v>
@@ -3860,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="J59" t="str">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K59" t="str">
         <v>0</v>
@@ -3872,7 +3872,7 @@
         <v>0</v>
       </c>
       <c r="N59" t="str">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O59" t="str">
         <v>일반</v>
@@ -3881,83 +3881,21 @@
         <v>-</v>
       </c>
       <c r="Q59" t="str">
-        <v>경기고속삼거리</v>
+        <v>분당구 구미동824-4</v>
       </c>
       <c r="R59" t="str">
         <v/>
       </c>
       <c r="S59" t="str">
-        <v>경기고속삼거리(탄천상로171)</v>
+        <v>강원철물건재 앞 도로(신수로787)</v>
       </c>
       <c r="T59" t="str">
-        <v>현장확인필요</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>26-21</v>
-      </c>
-      <c r="B60" t="str">
-        <v>대왕판교로</v>
-      </c>
-      <c r="C60" t="str">
-        <v>26-성남시-21</v>
-      </c>
-      <c r="D60" t="str">
-        <v>양호</v>
-      </c>
-      <c r="E60" t="str">
-        <v>종횡균열</v>
-      </c>
-      <c r="F60" t="str">
-        <v>양호</v>
-      </c>
-      <c r="G60" t="str">
-        <v>10.3</v>
-      </c>
-      <c r="H60" t="str">
-        <v>-</v>
-      </c>
-      <c r="I60" t="str">
-        <v>0</v>
-      </c>
-      <c r="J60" t="str">
-        <v>1</v>
-      </c>
-      <c r="K60" t="str">
-        <v>0</v>
-      </c>
-      <c r="L60" t="str">
-        <v>1</v>
-      </c>
-      <c r="M60" t="str">
-        <v>0</v>
-      </c>
-      <c r="N60" t="str">
-        <v>2</v>
-      </c>
-      <c r="O60" t="str">
-        <v>일반</v>
-      </c>
-      <c r="P60" t="str">
-        <v>-</v>
-      </c>
-      <c r="Q60" t="str">
-        <v>분당구 구미동824-4</v>
-      </c>
-      <c r="R60" t="str">
-        <v/>
-      </c>
-      <c r="S60" t="str">
-        <v>강원철물건재 앞 도로(신수로787)</v>
-      </c>
-      <c r="T60" t="str">
-        <v>현장확인필요</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:T59"/>
   </ignoredErrors>
 </worksheet>
 </file>